--- a/output1/LogisticRegression_val_predictions.xlsx
+++ b/output1/LogisticRegression_val_predictions.xlsx
@@ -497,7 +497,7 @@
         <v>0.9473684210526316</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3186176992165439</v>
+        <v>0.2717858548135437</v>
       </c>
     </row>
     <row r="3">
@@ -527,7 +527,7 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2950254721346117</v>
+        <v>0.2666641396815974</v>
       </c>
     </row>
     <row r="4">
@@ -557,7 +557,7 @@
         <v>3.342105263157895</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4801760806546172</v>
+        <v>0.4491595254690518</v>
       </c>
     </row>
     <row r="5">
@@ -587,7 +587,7 @@
         <v>0.5526315789473685</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6636104831917515</v>
+        <v>0.7056323192727991</v>
       </c>
     </row>
     <row r="6">
@@ -617,7 +617,7 @@
         <v>0.1052631578947368</v>
       </c>
       <c r="H6" t="n">
-        <v>0.004809321905715426</v>
+        <v>0.002836011316327738</v>
       </c>
     </row>
     <row r="7">
@@ -647,7 +647,7 @@
         <v>1.789473684210526</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6587163672663023</v>
+        <v>0.6477546680657938</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         <v>1.947368421052632</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3372349279262958</v>
+        <v>0.317052605720646</v>
       </c>
     </row>
     <row r="9">
@@ -707,7 +707,7 @@
         <v>1.421052631578947</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4378313177254579</v>
+        <v>0.436113104177286</v>
       </c>
     </row>
     <row r="10">
@@ -737,7 +737,7 @@
         <v>2.868421052631579</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3994749473000592</v>
+        <v>0.3288834017683119</v>
       </c>
     </row>
     <row r="11">
@@ -767,7 +767,7 @@
         <v>0.4736842105263157</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5642699753681512</v>
+        <v>0.5470031897207334</v>
       </c>
     </row>
     <row r="12">
@@ -797,7 +797,7 @@
         <v>2.894736842105264</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3571193693041709</v>
+        <v>0.3586077655161846</v>
       </c>
     </row>
     <row r="13">
@@ -824,10 +824,10 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>3.868421052631578</v>
+        <v>3.868421052631577</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4876271346678713</v>
+        <v>0.5435759841913935</v>
       </c>
     </row>
     <row r="14">
@@ -857,7 +857,7 @@
         <v>1.421052631578947</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3675600892319202</v>
+        <v>0.337982166466039</v>
       </c>
     </row>
     <row r="15">
@@ -887,7 +887,7 @@
         <v>7.657894736842105</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5720086142744283</v>
+        <v>0.506943435699584</v>
       </c>
     </row>
     <row r="16">
@@ -917,7 +917,7 @@
         <v>4.552631578947368</v>
       </c>
       <c r="H16" t="n">
-        <v>0.495857131799619</v>
+        <v>0.5197403072785315</v>
       </c>
     </row>
     <row r="17">
@@ -947,7 +947,7 @@
         <v>1.710526315789474</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2146998987401403</v>
+        <v>0.1935434681302123</v>
       </c>
     </row>
     <row r="18">
@@ -977,7 +977,7 @@
         <v>2.789473684210526</v>
       </c>
       <c r="H18" t="n">
-        <v>0.411364508010849</v>
+        <v>0.4033515389024874</v>
       </c>
     </row>
     <row r="19">
@@ -1007,7 +1007,7 @@
         <v>2.473684210526316</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7766744427345168</v>
+        <v>0.8138575126177487</v>
       </c>
     </row>
     <row r="20">
@@ -1037,7 +1037,7 @@
         <v>1.684210526315789</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2584768054365283</v>
+        <v>0.2411876732737704</v>
       </c>
     </row>
     <row r="21">
@@ -1067,7 +1067,7 @@
         <v>1.026315789473684</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4454115044148978</v>
+        <v>0.4337027688951971</v>
       </c>
     </row>
     <row r="22">
@@ -1097,7 +1097,7 @@
         <v>0.6842105263157895</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2491105703121136</v>
+        <v>0.3387252079608285</v>
       </c>
     </row>
     <row r="23">
@@ -1127,7 +1127,7 @@
         <v>3.131578947368421</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7782587344150972</v>
+        <v>0.791380885044897</v>
       </c>
     </row>
     <row r="24">
@@ -1157,7 +1157,7 @@
         <v>1.473684210526316</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4563875908157894</v>
+        <v>0.4590567071949659</v>
       </c>
     </row>
     <row r="25">
@@ -1187,7 +1187,7 @@
         <v>1.236842105263158</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5158679217193056</v>
+        <v>0.5501763432030364</v>
       </c>
     </row>
     <row r="26">
@@ -1217,7 +1217,7 @@
         <v>1.526315789473684</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7684063374007968</v>
+        <v>0.7932670667464686</v>
       </c>
     </row>
     <row r="27">
@@ -1247,7 +1247,7 @@
         <v>2.736842105263158</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3967616851666094</v>
+        <v>0.3880721109821628</v>
       </c>
     </row>
     <row r="28">
@@ -1277,7 +1277,7 @@
         <v>2.605263157894737</v>
       </c>
       <c r="H28" t="n">
-        <v>0.546090713838306</v>
+        <v>0.5429378046861945</v>
       </c>
     </row>
     <row r="29">
@@ -1307,7 +1307,7 @@
         <v>1.578947368421053</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4795068621419223</v>
+        <v>0.5045069891777879</v>
       </c>
     </row>
     <row r="30">
@@ -1337,7 +1337,7 @@
         <v>6.473684210526316</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5025437228614078</v>
+        <v>0.5212285661063379</v>
       </c>
     </row>
     <row r="31">
@@ -1367,7 +1367,7 @@
         <v>6.342105263157895</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4845132240764591</v>
+        <v>0.4926359291253132</v>
       </c>
     </row>
     <row r="32">
@@ -1397,7 +1397,7 @@
         <v>17.26315789473684</v>
       </c>
       <c r="H32" t="n">
-        <v>0.7659325396524885</v>
+        <v>0.7850874538910246</v>
       </c>
     </row>
     <row r="33">
@@ -1427,7 +1427,7 @@
         <v>15.60526315789474</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2299558822666793</v>
+        <v>0.1954796532986652</v>
       </c>
     </row>
     <row r="34">
@@ -1457,7 +1457,7 @@
         <v>21.68421052631579</v>
       </c>
       <c r="H34" t="n">
-        <v>0.4275979152039877</v>
+        <v>0.440486424550028</v>
       </c>
     </row>
     <row r="35">
@@ -1487,7 +1487,7 @@
         <v>14.26315789473684</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5063836166032623</v>
+        <v>0.5149134251398566</v>
       </c>
     </row>
     <row r="36">
@@ -1517,7 +1517,7 @@
         <v>1.894736842105263</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7125896048822842</v>
+        <v>0.7680114693662875</v>
       </c>
     </row>
     <row r="37">
@@ -1547,7 +1547,7 @@
         <v>0.2631578947368421</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1873089605847455</v>
+        <v>0.1717185418803895</v>
       </c>
     </row>
     <row r="38">
@@ -1577,7 +1577,7 @@
         <v>1.894736842105263</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3829073699646118</v>
+        <v>0.3550689600125798</v>
       </c>
     </row>
     <row r="39">
@@ -1607,7 +1607,7 @@
         <v>52.18421052631579</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5932506928691488</v>
+        <v>0.6236589840169371</v>
       </c>
     </row>
     <row r="40">
@@ -1637,7 +1637,7 @@
         <v>4.131578947368421</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5665409659088666</v>
+        <v>0.5690296088016765</v>
       </c>
     </row>
     <row r="41">
@@ -1667,7 +1667,7 @@
         <v>111.421052631579</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3354343443701547</v>
+        <v>0.3103088642665005</v>
       </c>
     </row>
     <row r="42">
@@ -1697,7 +1697,7 @@
         <v>15.02631578947368</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5340420750910152</v>
+        <v>0.5136944870962374</v>
       </c>
     </row>
     <row r="43">
@@ -1727,7 +1727,7 @@
         <v>19.34210526315789</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3516895191362753</v>
+        <v>0.3041252925586094</v>
       </c>
     </row>
     <row r="44">
@@ -1757,7 +1757,7 @@
         <v>46.63157894736842</v>
       </c>
       <c r="H44" t="n">
-        <v>0.4118410878263027</v>
+        <v>0.3913570513752364</v>
       </c>
     </row>
     <row r="45">
@@ -1787,7 +1787,7 @@
         <v>1.526315789473684</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2999581434934533</v>
+        <v>0.3121576718320751</v>
       </c>
     </row>
     <row r="46">
@@ -1817,7 +1817,7 @@
         <v>7.263157894736842</v>
       </c>
       <c r="H46" t="n">
-        <v>0.350528986242734</v>
+        <v>0.3477998837993785</v>
       </c>
     </row>
     <row r="47">
@@ -1847,7 +1847,7 @@
         <v>5.710526315789473</v>
       </c>
       <c r="H47" t="n">
-        <v>0.5398535118570341</v>
+        <v>0.5378219992418023</v>
       </c>
     </row>
     <row r="48">
@@ -1877,7 +1877,7 @@
         <v>4.394736842105263</v>
       </c>
       <c r="H48" t="n">
-        <v>0.4633944721409377</v>
+        <v>0.4823488349641</v>
       </c>
     </row>
     <row r="49">
@@ -1907,7 +1907,7 @@
         <v>0.7631578947368421</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1936811970734049</v>
+        <v>0.1682875415746839</v>
       </c>
     </row>
     <row r="50">
@@ -1937,7 +1937,7 @@
         <v>164.4473684210526</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2672811135193835</v>
+        <v>0.2162854597667167</v>
       </c>
     </row>
     <row r="51">
@@ -1967,7 +1967,7 @@
         <v>2.210526315789474</v>
       </c>
       <c r="H51" t="n">
-        <v>0.09833190816534611</v>
+        <v>0.08374188627870077</v>
       </c>
     </row>
     <row r="52">
@@ -1997,7 +1997,7 @@
         <v>1.947368421052632</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2076733884986132</v>
+        <v>0.1830436569188634</v>
       </c>
     </row>
     <row r="53">
@@ -2027,7 +2027,7 @@
         <v>3.184210526315789</v>
       </c>
       <c r="H53" t="n">
-        <v>0.6599692960819719</v>
+        <v>0.6738912733188651</v>
       </c>
     </row>
     <row r="54">
@@ -2057,7 +2057,7 @@
         <v>4.888268156424582</v>
       </c>
       <c r="H54" t="n">
-        <v>0.3571560373064838</v>
+        <v>0.2849970168241838</v>
       </c>
     </row>
     <row r="55">
@@ -2087,7 +2087,7 @@
         <v>2.067039106145252</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3404714410324828</v>
+        <v>0.295182858452063</v>
       </c>
     </row>
     <row r="56">
@@ -2117,7 +2117,7 @@
         <v>9.441340782122904</v>
       </c>
       <c r="H56" t="n">
-        <v>0.6192982795136545</v>
+        <v>0.6242098642515126</v>
       </c>
     </row>
     <row r="57">
@@ -2147,7 +2147,7 @@
         <v>4.804469273743017</v>
       </c>
       <c r="H57" t="n">
-        <v>0.6543562660482601</v>
+        <v>0.7741499434628492</v>
       </c>
     </row>
     <row r="58">
@@ -2177,7 +2177,7 @@
         <v>4.329608938547486</v>
       </c>
       <c r="H58" t="n">
-        <v>0.3117047667896448</v>
+        <v>0.2626171745952181</v>
       </c>
     </row>
     <row r="59">
@@ -2207,7 +2207,7 @@
         <v>9.441340782122904</v>
       </c>
       <c r="H59" t="n">
-        <v>0.5054833888641448</v>
+        <v>0.4775552696185705</v>
       </c>
     </row>
     <row r="60">
@@ -2237,7 +2237,7 @@
         <v>4.189944134078212</v>
       </c>
       <c r="H60" t="n">
-        <v>0.4307296833830022</v>
+        <v>0.3970614237834844</v>
       </c>
     </row>
     <row r="61">
@@ -2267,7 +2267,7 @@
         <v>5.363128491620112</v>
       </c>
       <c r="H61" t="n">
-        <v>0.234379628857492</v>
+        <v>0.1689295519324056</v>
       </c>
     </row>
     <row r="62">
@@ -2297,7 +2297,7 @@
         <v>21.08938547486034</v>
       </c>
       <c r="H62" t="n">
-        <v>0.69611984018232</v>
+        <v>0.7360202122429709</v>
       </c>
     </row>
     <row r="63">
@@ -2327,7 +2327,7 @@
         <v>28.46368715083799</v>
       </c>
       <c r="H63" t="n">
-        <v>0.6833893735637528</v>
+        <v>0.7140392190428941</v>
       </c>
     </row>
     <row r="64">
@@ -2357,7 +2357,7 @@
         <v>14.41340782122905</v>
       </c>
       <c r="H64" t="n">
-        <v>0.3079073291313053</v>
+        <v>0.2623959594984674</v>
       </c>
     </row>
     <row r="65">
@@ -2387,7 +2387,7 @@
         <v>25.19553072625699</v>
       </c>
       <c r="H65" t="n">
-        <v>0.6401299346928676</v>
+        <v>0.6635439339878485</v>
       </c>
     </row>
     <row r="66">
@@ -2417,7 +2417,7 @@
         <v>7.765363128491621</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2382285873089731</v>
+        <v>0.1779096929831334</v>
       </c>
     </row>
     <row r="67">
@@ -2447,7 +2447,7 @@
         <v>16.36871508379888</v>
       </c>
       <c r="H67" t="n">
-        <v>0.712691310046337</v>
+        <v>0.7395951865422838</v>
       </c>
     </row>
     <row r="68">
@@ -2477,7 +2477,7 @@
         <v>8</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0413359923699653</v>
+        <v>0.04027830994708093</v>
       </c>
     </row>
     <row r="69">
@@ -2507,7 +2507,7 @@
         <v>8</v>
       </c>
       <c r="H69" t="n">
-        <v>0.09730543672857753</v>
+        <v>0.1299082244755251</v>
       </c>
     </row>
     <row r="70">
@@ -2537,7 +2537,7 @@
         <v>10</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3159934564406532</v>
+        <v>0.4013249408526034</v>
       </c>
     </row>
     <row r="71">
@@ -2567,7 +2567,7 @@
         <v>38</v>
       </c>
       <c r="H71" t="n">
-        <v>0.9179357108997307</v>
+        <v>0.9048908720583695</v>
       </c>
     </row>
     <row r="72">
@@ -2597,7 +2597,7 @@
         <v>5</v>
       </c>
       <c r="H72" t="n">
-        <v>0.02933327683361787</v>
+        <v>0.02407826725584688</v>
       </c>
     </row>
     <row r="73">
@@ -2627,7 +2627,7 @@
         <v>19</v>
       </c>
       <c r="H73" t="n">
-        <v>0.311396870053299</v>
+        <v>0.3123156888878563</v>
       </c>
     </row>
     <row r="74">
@@ -2657,7 +2657,7 @@
         <v>16</v>
       </c>
       <c r="H74" t="n">
-        <v>0.3671832755617592</v>
+        <v>0.3775314391569892</v>
       </c>
     </row>
     <row r="75">
@@ -2687,7 +2687,7 @@
         <v>5</v>
       </c>
       <c r="H75" t="n">
-        <v>0.06669314097068794</v>
+        <v>0.05270834544600481</v>
       </c>
     </row>
     <row r="76">
@@ -2717,7 +2717,7 @@
         <v>8</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1808024804299465</v>
+        <v>0.1816175417479528</v>
       </c>
     </row>
     <row r="77">
@@ -2747,7 +2747,7 @@
         <v>13</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1842050624121658</v>
+        <v>0.1961998558925866</v>
       </c>
     </row>
     <row r="78">
@@ -2777,7 +2777,7 @@
         <v>8</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1850356550238967</v>
+        <v>0.1982767417248637</v>
       </c>
     </row>
     <row r="79">
@@ -2807,7 +2807,7 @@
         <v>6</v>
       </c>
       <c r="H79" t="n">
-        <v>0.2647289243260871</v>
+        <v>0.3134007353425572</v>
       </c>
     </row>
     <row r="80">
@@ -2837,7 +2837,7 @@
         <v>9</v>
       </c>
       <c r="H80" t="n">
-        <v>0.2706525832438483</v>
+        <v>0.2573661195539974</v>
       </c>
     </row>
     <row r="81">
@@ -2867,7 +2867,7 @@
         <v>8</v>
       </c>
       <c r="H81" t="n">
-        <v>0.1096834358130729</v>
+        <v>0.09877634964540701</v>
       </c>
     </row>
     <row r="82">
@@ -2897,7 +2897,7 @@
         <v>14</v>
       </c>
       <c r="H82" t="n">
-        <v>0.3318458576474767</v>
+        <v>0.2868520317686156</v>
       </c>
     </row>
     <row r="83">
@@ -2927,7 +2927,7 @@
         <v>8</v>
       </c>
       <c r="H83" t="n">
-        <v>0.03934697403013885</v>
+        <v>0.02799626848277668</v>
       </c>
     </row>
     <row r="84">
@@ -2957,7 +2957,7 @@
         <v>6</v>
       </c>
       <c r="H84" t="n">
-        <v>0.08615672271375296</v>
+        <v>0.06291382902399564</v>
       </c>
     </row>
     <row r="85">
@@ -2987,7 +2987,7 @@
         <v>5</v>
       </c>
       <c r="H85" t="n">
-        <v>0.08413517644797311</v>
+        <v>0.08960684608896961</v>
       </c>
     </row>
     <row r="86">
@@ -3017,7 +3017,7 @@
         <v>15</v>
       </c>
       <c r="H86" t="n">
-        <v>0.1230485983594945</v>
+        <v>0.09520254181170994</v>
       </c>
     </row>
     <row r="87">
@@ -3047,7 +3047,7 @@
         <v>8</v>
       </c>
       <c r="H87" t="n">
-        <v>0.08819839211906223</v>
+        <v>0.08488099637926007</v>
       </c>
     </row>
     <row r="88">
@@ -3077,7 +3077,7 @@
         <v>8</v>
       </c>
       <c r="H88" t="n">
-        <v>0.1525800552249384</v>
+        <v>0.1890245883414125</v>
       </c>
     </row>
     <row r="89">
@@ -3107,7 +3107,7 @@
         <v>10</v>
       </c>
       <c r="H89" t="n">
-        <v>0.2290067602810612</v>
+        <v>0.2463037275001745</v>
       </c>
     </row>
     <row r="90">
@@ -3137,7 +3137,7 @@
         <v>21</v>
       </c>
       <c r="H90" t="n">
-        <v>0.7250081388995417</v>
+        <v>0.7734376858296587</v>
       </c>
     </row>
     <row r="91">
@@ -3167,7 +3167,7 @@
         <v>8</v>
       </c>
       <c r="H91" t="n">
-        <v>0.05895419590805691</v>
+        <v>0.0420300421409681</v>
       </c>
     </row>
     <row r="92">
@@ -3197,7 +3197,7 @@
         <v>5</v>
       </c>
       <c r="H92" t="n">
-        <v>0.2421750269118446</v>
+        <v>0.2930202660010815</v>
       </c>
     </row>
     <row r="93">
@@ -3227,7 +3227,7 @@
         <v>4</v>
       </c>
       <c r="H93" t="n">
-        <v>0.1072131175698262</v>
+        <v>0.09836786622110674</v>
       </c>
     </row>
     <row r="94">
@@ -3257,7 +3257,7 @@
         <v>17</v>
       </c>
       <c r="H94" t="n">
-        <v>0.5003352396195606</v>
+        <v>0.4997299668535103</v>
       </c>
     </row>
     <row r="95">
@@ -3287,7 +3287,7 @@
         <v>6</v>
       </c>
       <c r="H95" t="n">
-        <v>0.1152259097244835</v>
+        <v>0.1067980649386418</v>
       </c>
     </row>
     <row r="96">
@@ -3317,7 +3317,7 @@
         <v>6</v>
       </c>
       <c r="H96" t="n">
-        <v>0.09143628403848671</v>
+        <v>0.09254986485376278</v>
       </c>
     </row>
     <row r="97">
@@ -3347,7 +3347,7 @@
         <v>8</v>
       </c>
       <c r="H97" t="n">
-        <v>0.5461061336411157</v>
+        <v>0.5160819654474789</v>
       </c>
     </row>
     <row r="98">
@@ -3377,7 +3377,7 @@
         <v>7</v>
       </c>
       <c r="H98" t="n">
-        <v>0.02308526980072912</v>
+        <v>0.01437709377254447</v>
       </c>
     </row>
     <row r="99">
@@ -3407,7 +3407,7 @@
         <v>8</v>
       </c>
       <c r="H99" t="n">
-        <v>0.04657859658720415</v>
+        <v>0.03758447606382317</v>
       </c>
     </row>
     <row r="100">
@@ -3437,7 +3437,7 @@
         <v>8</v>
       </c>
       <c r="H100" t="n">
-        <v>0.1395533327426164</v>
+        <v>0.1150404708068557</v>
       </c>
     </row>
     <row r="101">
@@ -3467,7 +3467,7 @@
         <v>8</v>
       </c>
       <c r="H101" t="n">
-        <v>0.09462566285925822</v>
+        <v>0.09318207298900832</v>
       </c>
     </row>
     <row r="102">
@@ -3497,7 +3497,7 @@
         <v>6</v>
       </c>
       <c r="H102" t="n">
-        <v>0.08731964366669188</v>
+        <v>0.06073979886900193</v>
       </c>
     </row>
     <row r="103">
@@ -3527,7 +3527,7 @@
         <v>49</v>
       </c>
       <c r="H103" t="n">
-        <v>0.9819457266038023</v>
+        <v>0.9854121760385994</v>
       </c>
     </row>
     <row r="104">
@@ -3557,7 +3557,7 @@
         <v>8</v>
       </c>
       <c r="H104" t="n">
-        <v>0.09093304060437546</v>
+        <v>0.1012592619606793</v>
       </c>
     </row>
     <row r="105">
@@ -3587,7 +3587,7 @@
         <v>11</v>
       </c>
       <c r="H105" t="n">
-        <v>0.06921255248731631</v>
+        <v>0.07078054340489261</v>
       </c>
     </row>
     <row r="106">
@@ -3617,7 +3617,7 @@
         <v>22</v>
       </c>
       <c r="H106" t="n">
-        <v>0.6418969024450002</v>
+        <v>0.6044999521636124</v>
       </c>
     </row>
     <row r="107">
@@ -3647,7 +3647,7 @@
         <v>19</v>
       </c>
       <c r="H107" t="n">
-        <v>0.1439746570133086</v>
+        <v>0.1785649312413755</v>
       </c>
     </row>
     <row r="108">
@@ -3677,7 +3677,7 @@
         <v>12</v>
       </c>
       <c r="H108" t="n">
-        <v>0.2014616120493432</v>
+        <v>0.2380947640108001</v>
       </c>
     </row>
     <row r="109">
@@ -3707,7 +3707,7 @@
         <v>8</v>
       </c>
       <c r="H109" t="n">
-        <v>0.090088998648844</v>
+        <v>0.09923190410655339</v>
       </c>
     </row>
     <row r="110">
@@ -3737,7 +3737,7 @@
         <v>3</v>
       </c>
       <c r="H110" t="n">
-        <v>0.1982970604125078</v>
+        <v>0.2010529572416132</v>
       </c>
     </row>
     <row r="111">
@@ -3767,7 +3767,7 @@
         <v>11</v>
       </c>
       <c r="H111" t="n">
-        <v>0.403707261846944</v>
+        <v>0.4591415010187737</v>
       </c>
     </row>
     <row r="112">
@@ -3797,7 +3797,7 @@
         <v>7</v>
       </c>
       <c r="H112" t="n">
-        <v>0.1578636761832594</v>
+        <v>0.1272808017329923</v>
       </c>
     </row>
     <row r="113">
@@ -3827,7 +3827,7 @@
         <v>8</v>
       </c>
       <c r="H113" t="n">
-        <v>0.298928885342882</v>
+        <v>0.2629872923258162</v>
       </c>
     </row>
     <row r="114">
@@ -3857,7 +3857,7 @@
         <v>9</v>
       </c>
       <c r="H114" t="n">
-        <v>0.09631533964378598</v>
+        <v>0.07980445355520485</v>
       </c>
     </row>
     <row r="115">
@@ -3887,7 +3887,7 @@
         <v>35</v>
       </c>
       <c r="H115" t="n">
-        <v>0.8383858226643021</v>
+        <v>0.8352403238301048</v>
       </c>
     </row>
     <row r="116">
@@ -3917,7 +3917,7 @@
         <v>5</v>
       </c>
       <c r="H116" t="n">
-        <v>0.2409176715692141</v>
+        <v>0.2436760521208948</v>
       </c>
     </row>
     <row r="117">
@@ -3947,7 +3947,7 @@
         <v>5</v>
       </c>
       <c r="H117" t="n">
-        <v>0.6778783950496309</v>
+        <v>0.7044315522846674</v>
       </c>
     </row>
     <row r="118">
@@ -3977,7 +3977,7 @@
         <v>3</v>
       </c>
       <c r="H118" t="n">
-        <v>0.04046851038447619</v>
+        <v>0.02650408198471086</v>
       </c>
     </row>
     <row r="119">
@@ -4007,7 +4007,7 @@
         <v>8</v>
       </c>
       <c r="H119" t="n">
-        <v>0.1136048401757744</v>
+        <v>0.09651992970081412</v>
       </c>
     </row>
     <row r="120">
@@ -4037,7 +4037,7 @@
         <v>8</v>
       </c>
       <c r="H120" t="n">
-        <v>0.139369266495936</v>
+        <v>0.1147326366703187</v>
       </c>
     </row>
     <row r="121">
@@ -4067,7 +4067,7 @@
         <v>8</v>
       </c>
       <c r="H121" t="n">
-        <v>0.05418304303469144</v>
+        <v>0.03779274870200622</v>
       </c>
     </row>
     <row r="122">
@@ -4097,7 +4097,7 @@
         <v>5</v>
       </c>
       <c r="H122" t="n">
-        <v>0.09802972510587214</v>
+        <v>0.07889227272871856</v>
       </c>
     </row>
     <row r="123">
@@ -4127,7 +4127,7 @@
         <v>8</v>
       </c>
       <c r="H123" t="n">
-        <v>0.2093418538568572</v>
+        <v>0.2607618982624954</v>
       </c>
     </row>
     <row r="124">
@@ -4157,7 +4157,7 @@
         <v>14</v>
       </c>
       <c r="H124" t="n">
-        <v>0.6722181863233292</v>
+        <v>0.7005383204052834</v>
       </c>
     </row>
     <row r="125">
@@ -4187,7 +4187,7 @@
         <v>4</v>
       </c>
       <c r="H125" t="n">
-        <v>0.08008029325828495</v>
+        <v>0.05305165895561089</v>
       </c>
     </row>
     <row r="126">
@@ -4217,7 +4217,7 @@
         <v>7</v>
       </c>
       <c r="H126" t="n">
-        <v>0.2688150377275944</v>
+        <v>0.2466408087561814</v>
       </c>
     </row>
     <row r="127">
@@ -4247,7 +4247,7 @@
         <v>10</v>
       </c>
       <c r="H127" t="n">
-        <v>0.07078574967304825</v>
+        <v>0.05050066276502254</v>
       </c>
     </row>
     <row r="128">
@@ -4277,7 +4277,7 @@
         <v>0.8947368421052632</v>
       </c>
       <c r="H128" t="n">
-        <v>0.311283606890349</v>
+        <v>0.1959229973382936</v>
       </c>
     </row>
     <row r="129">
@@ -4307,7 +4307,7 @@
         <v>1.157894736842105</v>
       </c>
       <c r="H129" t="n">
-        <v>0.323608284530271</v>
+        <v>0.3410690533727122</v>
       </c>
     </row>
     <row r="130">
@@ -4337,7 +4337,7 @@
         <v>1.105263157894737</v>
       </c>
       <c r="H130" t="n">
-        <v>0.7794513150202372</v>
+        <v>0.8205886922838652</v>
       </c>
     </row>
     <row r="131">
@@ -4367,7 +4367,7 @@
         <v>1.921052631578948</v>
       </c>
       <c r="H131" t="n">
-        <v>0.7196737209279067</v>
+        <v>0.780868804442086</v>
       </c>
     </row>
     <row r="132">
@@ -4397,7 +4397,7 @@
         <v>0.6578947368421053</v>
       </c>
       <c r="H132" t="n">
-        <v>0.3589084892186023</v>
+        <v>0.368692703106596</v>
       </c>
     </row>
     <row r="133">
@@ -4427,7 +4427,7 @@
         <v>0.1052631578947368</v>
       </c>
       <c r="H133" t="n">
-        <v>0.7259368042181472</v>
+        <v>0.8013556045304941</v>
       </c>
     </row>
     <row r="134">
@@ -4457,7 +4457,7 @@
         <v>1.526315789473684</v>
       </c>
       <c r="H134" t="n">
-        <v>0.1899360819540465</v>
+        <v>0.2000655117293855</v>
       </c>
     </row>
     <row r="135">
@@ -4487,7 +4487,7 @@
         <v>0.631578947368421</v>
       </c>
       <c r="H135" t="n">
-        <v>0.4430735168208753</v>
+        <v>0.4419102171318899</v>
       </c>
     </row>
     <row r="136">
@@ -4517,7 +4517,7 @@
         <v>1.789473684210526</v>
       </c>
       <c r="H136" t="n">
-        <v>0.1119489122723471</v>
+        <v>0.09569803801060393</v>
       </c>
     </row>
     <row r="137">
@@ -4547,7 +4547,7 @@
         <v>1.447368421052632</v>
       </c>
       <c r="H137" t="n">
-        <v>0.1750375233107131</v>
+        <v>0.1330621410839339</v>
       </c>
     </row>
     <row r="138">
@@ -4577,7 +4577,7 @@
         <v>4.657894736842105</v>
       </c>
       <c r="H138" t="n">
-        <v>0.7673309180382476</v>
+        <v>0.7683050219106</v>
       </c>
     </row>
     <row r="139">
@@ -4607,7 +4607,7 @@
         <v>1.710526315789474</v>
       </c>
       <c r="H139" t="n">
-        <v>0.79568826724084</v>
+        <v>0.8406889019878703</v>
       </c>
     </row>
     <row r="140">
@@ -4637,7 +4637,7 @@
         <v>1.368421052631579</v>
       </c>
       <c r="H140" t="n">
-        <v>0.6715476646498869</v>
+        <v>0.7217719905713995</v>
       </c>
     </row>
     <row r="141">
@@ -4667,7 +4667,7 @@
         <v>2.763157894736842</v>
       </c>
       <c r="H141" t="n">
-        <v>0.420939433312493</v>
+        <v>0.4472045757130123</v>
       </c>
     </row>
     <row r="142">
@@ -4697,7 +4697,7 @@
         <v>1.131578947368421</v>
       </c>
       <c r="H142" t="n">
-        <v>0.3827329406933604</v>
+        <v>0.3524257736464646</v>
       </c>
     </row>
     <row r="143">
@@ -4727,7 +4727,7 @@
         <v>1.552631578947368</v>
       </c>
       <c r="H143" t="n">
-        <v>0.3000906611598124</v>
+        <v>0.2709424697964763</v>
       </c>
     </row>
     <row r="144">
@@ -4757,7 +4757,7 @@
         <v>1.368421052631579</v>
       </c>
       <c r="H144" t="n">
-        <v>0.1791153853063658</v>
+        <v>0.1673881863295183</v>
       </c>
     </row>
     <row r="145">
@@ -4787,7 +4787,7 @@
         <v>0.9736842105263158</v>
       </c>
       <c r="H145" t="n">
-        <v>0.2424632906380018</v>
+        <v>0.1997371879335456</v>
       </c>
     </row>
     <row r="146">
@@ -4817,7 +4817,7 @@
         <v>0.7368421052631579</v>
       </c>
       <c r="H146" t="n">
-        <v>0.449046134774964</v>
+        <v>0.3638555943142597</v>
       </c>
     </row>
     <row r="147">
@@ -4847,7 +4847,7 @@
         <v>1.684210526315789</v>
       </c>
       <c r="H147" t="n">
-        <v>0.7178114019217805</v>
+        <v>0.7599307946153819</v>
       </c>
     </row>
     <row r="148">
@@ -4877,7 +4877,7 @@
         <v>1.947368421052632</v>
       </c>
       <c r="H148" t="n">
-        <v>0.3458653172940911</v>
+        <v>0.316983444214174</v>
       </c>
     </row>
     <row r="149">
@@ -4907,7 +4907,7 @@
         <v>1.078947368421053</v>
       </c>
       <c r="H149" t="n">
-        <v>0.6635977174909593</v>
+        <v>0.7095763683632773</v>
       </c>
     </row>
     <row r="150">
@@ -4937,7 +4937,7 @@
         <v>0.8947368421052632</v>
       </c>
       <c r="H150" t="n">
-        <v>0.08001121398778896</v>
+        <v>0.06735416886940869</v>
       </c>
     </row>
     <row r="151">
@@ -4967,7 +4967,7 @@
         <v>1.631578947368421</v>
       </c>
       <c r="H151" t="n">
-        <v>0.1158933999345644</v>
+        <v>0.1070515167540395</v>
       </c>
     </row>
     <row r="152">
@@ -4997,7 +4997,7 @@
         <v>1.789473684210526</v>
       </c>
       <c r="H152" t="n">
-        <v>0.6318031744833952</v>
+        <v>0.6435117267565981</v>
       </c>
     </row>
     <row r="153">
@@ -5027,7 +5027,7 @@
         <v>0.9473684210526316</v>
       </c>
       <c r="H153" t="n">
-        <v>0.7215425495402215</v>
+        <v>0.6841988914268199</v>
       </c>
     </row>
     <row r="154">
@@ -5057,7 +5057,7 @@
         <v>1.868421052631579</v>
       </c>
       <c r="H154" t="n">
-        <v>0.56162562805391</v>
+        <v>0.5820232100767435</v>
       </c>
     </row>
     <row r="155">
@@ -5087,7 +5087,7 @@
         <v>2.5</v>
       </c>
       <c r="H155" t="n">
-        <v>0.2360820024279104</v>
+        <v>0.2249174434461504</v>
       </c>
     </row>
     <row r="156">
@@ -5117,7 +5117,7 @@
         <v>0.5789473684210527</v>
       </c>
       <c r="H156" t="n">
-        <v>0.07915502076533432</v>
+        <v>0.06556885204854632</v>
       </c>
     </row>
     <row r="157">
@@ -5147,7 +5147,7 @@
         <v>1.184210526315789</v>
       </c>
       <c r="H157" t="n">
-        <v>0.2695431644290313</v>
+        <v>0.2454194244166351</v>
       </c>
     </row>
     <row r="158">
@@ -5177,7 +5177,7 @@
         <v>8.631578947368421</v>
       </c>
       <c r="H158" t="n">
-        <v>0.8129605242168226</v>
+        <v>0.8332129875720774</v>
       </c>
     </row>
     <row r="159">
@@ -5207,7 +5207,7 @@
         <v>0.7894736842105263</v>
       </c>
       <c r="H159" t="n">
-        <v>0.5027083234031265</v>
+        <v>0.5250037411975017</v>
       </c>
     </row>
     <row r="160">
@@ -5237,7 +5237,7 @@
         <v>54.6578947368421</v>
       </c>
       <c r="H160" t="n">
-        <v>0.7103027454380602</v>
+        <v>0.7454256995697611</v>
       </c>
     </row>
     <row r="161">
@@ -5267,7 +5267,7 @@
         <v>1.578947368421053</v>
       </c>
       <c r="H161" t="n">
-        <v>0.369221663170991</v>
+        <v>0.3563210139477992</v>
       </c>
     </row>
     <row r="162">
@@ -5297,7 +5297,7 @@
         <v>4.789473684210527</v>
       </c>
       <c r="H162" t="n">
-        <v>0.6194181912670941</v>
+        <v>0.6379291449193181</v>
       </c>
     </row>
     <row r="163">
@@ -5327,7 +5327,7 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="H163" t="n">
-        <v>0.4779121731415245</v>
+        <v>0.5116431462047742</v>
       </c>
     </row>
     <row r="164">
@@ -5357,7 +5357,7 @@
         <v>5.315789473684211</v>
       </c>
       <c r="H164" t="n">
-        <v>0.1942980019005851</v>
+        <v>0.1688031381969407</v>
       </c>
     </row>
     <row r="165">
@@ -5387,7 +5387,7 @@
         <v>41.21052631578947</v>
       </c>
       <c r="H165" t="n">
-        <v>0.9380845340925377</v>
+        <v>0.9578534189707504</v>
       </c>
     </row>
     <row r="166">
@@ -5417,7 +5417,7 @@
         <v>5.289473684210527</v>
       </c>
       <c r="H166" t="n">
-        <v>0.1556565019781499</v>
+        <v>0.1105278170132343</v>
       </c>
     </row>
     <row r="167">
@@ -5447,7 +5447,7 @@
         <v>9</v>
       </c>
       <c r="H167" t="n">
-        <v>0.6595544149996075</v>
+        <v>0.6996592305456564</v>
       </c>
     </row>
     <row r="168">
@@ -5477,7 +5477,7 @@
         <v>3.5</v>
       </c>
       <c r="H168" t="n">
-        <v>0.6054243480929039</v>
+        <v>0.6228484830570793</v>
       </c>
     </row>
     <row r="169">
@@ -5507,7 +5507,7 @@
         <v>1.526315789473684</v>
       </c>
       <c r="H169" t="n">
-        <v>0.2055937967418045</v>
+        <v>0.1662305254753651</v>
       </c>
     </row>
     <row r="170">
@@ -5537,7 +5537,7 @@
         <v>15.05263157894737</v>
       </c>
       <c r="H170" t="n">
-        <v>0.6889099010224408</v>
+        <v>0.6600469276600507</v>
       </c>
     </row>
     <row r="171">
@@ -5567,7 +5567,7 @@
         <v>8.631578947368421</v>
       </c>
       <c r="H171" t="n">
-        <v>0.8591723519916874</v>
+        <v>0.8615888121120407</v>
       </c>
     </row>
     <row r="172">
@@ -5597,7 +5597,7 @@
         <v>0.2631578947368421</v>
       </c>
       <c r="H172" t="n">
-        <v>0.8312464750926056</v>
+        <v>0.8530269183932452</v>
       </c>
     </row>
     <row r="173">
@@ -5627,7 +5627,7 @@
         <v>0.4736842105263157</v>
       </c>
       <c r="H173" t="n">
-        <v>0.6580054204728862</v>
+        <v>0.6997844908641289</v>
       </c>
     </row>
     <row r="174">
@@ -5657,7 +5657,7 @@
         <v>1.684210526315789</v>
       </c>
       <c r="H174" t="n">
-        <v>0.1459121782201036</v>
+        <v>0.1293231397792874</v>
       </c>
     </row>
     <row r="175">
@@ -5687,7 +5687,7 @@
         <v>7.710526315789473</v>
       </c>
       <c r="H175" t="n">
-        <v>0.3972569652504047</v>
+        <v>0.348848151027653</v>
       </c>
     </row>
     <row r="176">
@@ -5717,7 +5717,7 @@
         <v>0.4473684210526316</v>
       </c>
       <c r="H176" t="n">
-        <v>0.8969854103755976</v>
+        <v>0.927679407849784</v>
       </c>
     </row>
     <row r="177">
@@ -5747,7 +5747,7 @@
         <v>55.71052631578947</v>
       </c>
       <c r="H177" t="n">
-        <v>0.4298780507532785</v>
+        <v>0.4269337865237989</v>
       </c>
     </row>
     <row r="178">
@@ -5777,7 +5777,7 @@
         <v>7.342105263157895</v>
       </c>
       <c r="H178" t="n">
-        <v>0.8198350656707922</v>
+        <v>0.8471160644478026</v>
       </c>
     </row>
     <row r="179">
@@ -5807,7 +5807,7 @@
         <v>17.07894736842105</v>
       </c>
       <c r="H179" t="n">
-        <v>0.5003682787266185</v>
+        <v>0.5027559999718763</v>
       </c>
     </row>
     <row r="180">
@@ -5837,7 +5837,7 @@
         <v>9.441340782122904</v>
       </c>
       <c r="H180" t="n">
-        <v>0.2413309358193925</v>
+        <v>0.1793244168020836</v>
       </c>
     </row>
     <row r="181">
@@ -5867,7 +5867,7 @@
         <v>9.441340782122904</v>
       </c>
       <c r="H181" t="n">
-        <v>0.5474507255729493</v>
+        <v>0.5802118187367616</v>
       </c>
     </row>
     <row r="182">
@@ -5897,7 +5897,7 @@
         <v>17.40223463687151</v>
       </c>
       <c r="H182" t="n">
-        <v>0.828503701572371</v>
+        <v>0.9035951710748957</v>
       </c>
     </row>
     <row r="183">
@@ -5927,7 +5927,7 @@
         <v>9.441340782122904</v>
       </c>
       <c r="H183" t="n">
-        <v>0.399527080386625</v>
+        <v>0.3813101452879866</v>
       </c>
     </row>
     <row r="184">
@@ -5957,7 +5957,7 @@
         <v>7.178770949720671</v>
       </c>
       <c r="H184" t="n">
-        <v>0.4564316149252858</v>
+        <v>0.3818119286673545</v>
       </c>
     </row>
     <row r="185">
@@ -5987,7 +5987,7 @@
         <v>7.011173184357543</v>
       </c>
       <c r="H185" t="n">
-        <v>0.4302580048595508</v>
+        <v>0.3861730706966303</v>
       </c>
     </row>
     <row r="186">
@@ -6017,7 +6017,7 @@
         <v>11.95530726256983</v>
       </c>
       <c r="H186" t="n">
-        <v>0.2411286198990753</v>
+        <v>0.1765135668947246</v>
       </c>
     </row>
     <row r="187">
@@ -6047,7 +6047,7 @@
         <v>0.6983240223463688</v>
       </c>
       <c r="H187" t="n">
-        <v>0.4748659316356728</v>
+        <v>0.4822780775358735</v>
       </c>
     </row>
     <row r="188">
@@ -6077,7 +6077,7 @@
         <v>46.08938547486034</v>
       </c>
       <c r="H188" t="n">
-        <v>0.7810173017015117</v>
+        <v>0.8176700981155172</v>
       </c>
     </row>
     <row r="189">
@@ -6107,7 +6107,7 @@
         <v>2.067039106145252</v>
       </c>
       <c r="H189" t="n">
-        <v>0.2042593876001739</v>
+        <v>0.1573552212803536</v>
       </c>
     </row>
     <row r="190">
@@ -6137,7 +6137,7 @@
         <v>35.81005586592179</v>
       </c>
       <c r="H190" t="n">
-        <v>0.8470046496187603</v>
+        <v>0.8774444137665136</v>
       </c>
     </row>
     <row r="191">
@@ -6167,7 +6167,7 @@
         <v>7.178770949720671</v>
       </c>
       <c r="H191" t="n">
-        <v>0.4598996720063329</v>
+        <v>0.4643058638310498</v>
       </c>
     </row>
     <row r="192">
@@ -6197,7 +6197,7 @@
         <v>6.843575418994414</v>
       </c>
       <c r="H192" t="n">
-        <v>0.8840409942044372</v>
+        <v>0.9292106188167872</v>
       </c>
     </row>
     <row r="193">
@@ -6227,7 +6227,7 @@
         <v>1.871508379888268</v>
       </c>
       <c r="H193" t="n">
-        <v>0.2556464562617335</v>
+        <v>0.2644102741582974</v>
       </c>
     </row>
     <row r="194">
@@ -6257,7 +6257,7 @@
         <v>18</v>
       </c>
       <c r="H194" t="n">
-        <v>0.4425663374999046</v>
+        <v>0.3093618985511333</v>
       </c>
     </row>
     <row r="195">
@@ -6287,7 +6287,7 @@
         <v>8</v>
       </c>
       <c r="H195" t="n">
-        <v>0.371387043783689</v>
+        <v>0.496287147718439</v>
       </c>
     </row>
     <row r="196">
@@ -6317,7 +6317,7 @@
         <v>18</v>
       </c>
       <c r="H196" t="n">
-        <v>0.4411095698143987</v>
+        <v>0.3705136399585811</v>
       </c>
     </row>
     <row r="197">
@@ -6347,7 +6347,7 @@
         <v>2</v>
       </c>
       <c r="H197" t="n">
-        <v>0.1975010883002601</v>
+        <v>0.2570249120974464</v>
       </c>
     </row>
     <row r="198">
@@ -6377,7 +6377,7 @@
         <v>8</v>
       </c>
       <c r="H198" t="n">
-        <v>0.269439026089663</v>
+        <v>0.2070939876922166</v>
       </c>
     </row>
     <row r="199">
@@ -6407,7 +6407,7 @@
         <v>9</v>
       </c>
       <c r="H199" t="n">
-        <v>0.4677316609484133</v>
+        <v>0.4362811936584919</v>
       </c>
     </row>
     <row r="200">
@@ -6437,7 +6437,7 @@
         <v>21</v>
       </c>
       <c r="H200" t="n">
-        <v>0.4152247125787409</v>
+        <v>0.4355286840856175</v>
       </c>
     </row>
     <row r="201">
@@ -6467,7 +6467,7 @@
         <v>8</v>
       </c>
       <c r="H201" t="n">
-        <v>0.1340221763169164</v>
+        <v>0.1636142384643547</v>
       </c>
     </row>
     <row r="202">
@@ -6497,7 +6497,7 @@
         <v>5</v>
       </c>
       <c r="H202" t="n">
-        <v>0.1126740270796612</v>
+        <v>0.06562277709673212</v>
       </c>
     </row>
     <row r="203">
@@ -6527,7 +6527,7 @@
         <v>8</v>
       </c>
       <c r="H203" t="n">
-        <v>0.3213733336667691</v>
+        <v>0.2784283778146296</v>
       </c>
     </row>
     <row r="204">
@@ -6557,7 +6557,7 @@
         <v>2</v>
       </c>
       <c r="H204" t="n">
-        <v>0.09508432388544541</v>
+        <v>0.07481337892413234</v>
       </c>
     </row>
     <row r="205">
@@ -6587,7 +6587,7 @@
         <v>20</v>
       </c>
       <c r="H205" t="n">
-        <v>0.4573321156414684</v>
+        <v>0.5115118546492387</v>
       </c>
     </row>
     <row r="206">
@@ -6617,7 +6617,7 @@
         <v>5</v>
       </c>
       <c r="H206" t="n">
-        <v>0.05172617521107108</v>
+        <v>0.03512105039434724</v>
       </c>
     </row>
     <row r="207">
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="H207" t="n">
-        <v>0.2910107391009636</v>
+        <v>0.2839745085958074</v>
       </c>
     </row>
     <row r="208">
@@ -6677,7 +6677,7 @@
         <v>1</v>
       </c>
       <c r="H208" t="n">
-        <v>0.04854786216748801</v>
+        <v>0.04020322922214061</v>
       </c>
     </row>
     <row r="209">
@@ -6707,7 +6707,7 @@
         <v>8</v>
       </c>
       <c r="H209" t="n">
-        <v>0.02456346903548824</v>
+        <v>0.0280239502600608</v>
       </c>
     </row>
     <row r="210">
@@ -6737,7 +6737,7 @@
         <v>13</v>
       </c>
       <c r="H210" t="n">
-        <v>0.2641026003051575</v>
+        <v>0.3614819951007143</v>
       </c>
     </row>
     <row r="211">
@@ -6767,7 +6767,7 @@
         <v>2</v>
       </c>
       <c r="H211" t="n">
-        <v>0.186223294343316</v>
+        <v>0.2379121350791017</v>
       </c>
     </row>
     <row r="212">
@@ -6797,7 +6797,7 @@
         <v>7</v>
       </c>
       <c r="H212" t="n">
-        <v>0.05244114826286744</v>
+        <v>0.0296566667101486</v>
       </c>
     </row>
     <row r="213">
@@ -6827,7 +6827,7 @@
         <v>7</v>
       </c>
       <c r="H213" t="n">
-        <v>0.3130129362267421</v>
+        <v>0.2071464158531844</v>
       </c>
     </row>
     <row r="214">
@@ -6857,7 +6857,7 @@
         <v>2</v>
       </c>
       <c r="H214" t="n">
-        <v>0.09800924715310268</v>
+        <v>0.06306142882472641</v>
       </c>
     </row>
     <row r="215">
@@ -6887,7 +6887,7 @@
         <v>8</v>
       </c>
       <c r="H215" t="n">
-        <v>0.3845174692890982</v>
+        <v>0.5207953411291333</v>
       </c>
     </row>
     <row r="216">
@@ -6917,7 +6917,7 @@
         <v>6</v>
       </c>
       <c r="H216" t="n">
-        <v>0.01428225562354101</v>
+        <v>0.01224755861245697</v>
       </c>
     </row>
     <row r="217">
@@ -6947,7 +6947,7 @@
         <v>8</v>
       </c>
       <c r="H217" t="n">
-        <v>0.08781611595577016</v>
+        <v>0.07683260961659789</v>
       </c>
     </row>
     <row r="218">
@@ -6977,7 +6977,7 @@
         <v>8</v>
       </c>
       <c r="H218" t="n">
-        <v>0.06165890687330724</v>
+        <v>0.06614890198471972</v>
       </c>
     </row>
     <row r="219">
@@ -7007,7 +7007,7 @@
         <v>8</v>
       </c>
       <c r="H219" t="n">
-        <v>0.09029472038093736</v>
+        <v>0.1043410493064177</v>
       </c>
     </row>
     <row r="220">
@@ -7037,7 +7037,7 @@
         <v>14</v>
       </c>
       <c r="H220" t="n">
-        <v>0.05145332352952903</v>
+        <v>0.03865092896297578</v>
       </c>
     </row>
     <row r="221">
@@ -7067,7 +7067,7 @@
         <v>5</v>
       </c>
       <c r="H221" t="n">
-        <v>0.1410197179220709</v>
+        <v>0.2691291817924971</v>
       </c>
     </row>
     <row r="222">
@@ -7097,7 +7097,7 @@
         <v>20</v>
       </c>
       <c r="H222" t="n">
-        <v>0.2037093035630808</v>
+        <v>0.2061981168725136</v>
       </c>
     </row>
     <row r="223">
@@ -7127,7 +7127,7 @@
         <v>3</v>
       </c>
       <c r="H223" t="n">
-        <v>0.1349220819381588</v>
+        <v>0.2014646901264289</v>
       </c>
     </row>
     <row r="224">
@@ -7157,7 +7157,7 @@
         <v>8</v>
       </c>
       <c r="H224" t="n">
-        <v>0.231828238952549</v>
+        <v>0.2051964262860118</v>
       </c>
     </row>
     <row r="225">
@@ -7187,7 +7187,7 @@
         <v>17</v>
       </c>
       <c r="H225" t="n">
-        <v>0.2529739665847799</v>
+        <v>0.2488484237901473</v>
       </c>
     </row>
     <row r="226">
@@ -7217,7 +7217,7 @@
         <v>12</v>
       </c>
       <c r="H226" t="n">
-        <v>0.1008839834923402</v>
+        <v>0.1000288705189261</v>
       </c>
     </row>
     <row r="227">
@@ -7247,7 +7247,7 @@
         <v>5</v>
       </c>
       <c r="H227" t="n">
-        <v>0.119595890862193</v>
+        <v>0.1203313256436222</v>
       </c>
     </row>
     <row r="228">
@@ -7277,7 +7277,7 @@
         <v>7</v>
       </c>
       <c r="H228" t="n">
-        <v>0.12652193248384</v>
+        <v>0.1061158293505492</v>
       </c>
     </row>
     <row r="229">
@@ -7307,7 +7307,7 @@
         <v>14</v>
       </c>
       <c r="H229" t="n">
-        <v>0.4966206175174052</v>
+        <v>0.5685754594417606</v>
       </c>
     </row>
     <row r="230">
@@ -7337,7 +7337,7 @@
         <v>12</v>
       </c>
       <c r="H230" t="n">
-        <v>0.2308241344770395</v>
+        <v>0.2678042993756568</v>
       </c>
     </row>
     <row r="231">
@@ -7367,7 +7367,7 @@
         <v>8</v>
       </c>
       <c r="H231" t="n">
-        <v>0.5924559700079444</v>
+        <v>0.5802663676838797</v>
       </c>
     </row>
     <row r="232">
@@ -7397,7 +7397,7 @@
         <v>4</v>
       </c>
       <c r="H232" t="n">
-        <v>0.07011143437621004</v>
+        <v>0.1103479770933575</v>
       </c>
     </row>
     <row r="233">
@@ -7427,7 +7427,7 @@
         <v>6</v>
       </c>
       <c r="H233" t="n">
-        <v>0.1472018023948239</v>
+        <v>0.1465559387505288</v>
       </c>
     </row>
     <row r="234">
@@ -7457,7 +7457,7 @@
         <v>18</v>
       </c>
       <c r="H234" t="n">
-        <v>0.4499453052421688</v>
+        <v>0.4470116494162156</v>
       </c>
     </row>
     <row r="235">
@@ -7487,7 +7487,7 @@
         <v>8</v>
       </c>
       <c r="H235" t="n">
-        <v>0.0807160318114218</v>
+        <v>0.07606084981213662</v>
       </c>
     </row>
     <row r="236">
@@ -7517,7 +7517,7 @@
         <v>18</v>
       </c>
       <c r="H236" t="n">
-        <v>0.1294513747500803</v>
+        <v>0.1415078849979066</v>
       </c>
     </row>
     <row r="237">
@@ -7547,7 +7547,7 @@
         <v>35</v>
       </c>
       <c r="H237" t="n">
-        <v>0.7918688138165741</v>
+        <v>0.7863228405274408</v>
       </c>
     </row>
     <row r="238">
@@ -7577,7 +7577,7 @@
         <v>5</v>
       </c>
       <c r="H238" t="n">
-        <v>0.2258405892595175</v>
+        <v>0.2895088929335241</v>
       </c>
     </row>
     <row r="239">
@@ -7607,7 +7607,7 @@
         <v>3</v>
       </c>
       <c r="H239" t="n">
-        <v>0.1208249263034337</v>
+        <v>0.1710776702901128</v>
       </c>
     </row>
     <row r="240">
@@ -7637,7 +7637,7 @@
         <v>22</v>
       </c>
       <c r="H240" t="n">
-        <v>0.1757744650352248</v>
+        <v>0.1416496420335</v>
       </c>
     </row>
     <row r="241">
@@ -7667,7 +7667,7 @@
         <v>8</v>
       </c>
       <c r="H241" t="n">
-        <v>0.04516672835883816</v>
+        <v>0.04397184450404953</v>
       </c>
     </row>
     <row r="242">
@@ -7697,7 +7697,7 @@
         <v>15</v>
       </c>
       <c r="H242" t="n">
-        <v>0.2103247107924171</v>
+        <v>0.2854303988617007</v>
       </c>
     </row>
     <row r="243">
@@ -7727,7 +7727,7 @@
         <v>14</v>
       </c>
       <c r="H243" t="n">
-        <v>0.3200369089429839</v>
+        <v>0.2954339691793617</v>
       </c>
     </row>
     <row r="244">
@@ -7757,7 +7757,7 @@
         <v>10</v>
       </c>
       <c r="H244" t="n">
-        <v>0.05524992023316067</v>
+        <v>0.03011105670513947</v>
       </c>
     </row>
     <row r="245">
@@ -7787,7 +7787,7 @@
         <v>14</v>
       </c>
       <c r="H245" t="n">
-        <v>0.3087988560032146</v>
+        <v>0.407701418338676</v>
       </c>
     </row>
     <row r="246">
@@ -7817,7 +7817,7 @@
         <v>17</v>
       </c>
       <c r="H246" t="n">
-        <v>0.1474908134591669</v>
+        <v>0.1860902772004029</v>
       </c>
     </row>
     <row r="247">
@@ -7847,7 +7847,7 @@
         <v>6</v>
       </c>
       <c r="H247" t="n">
-        <v>0.1009448616301488</v>
+        <v>0.05505803030299487</v>
       </c>
     </row>
     <row r="248">
@@ -7877,7 +7877,7 @@
         <v>9</v>
       </c>
       <c r="H248" t="n">
-        <v>0.05785247626608119</v>
+        <v>0.05336278084921722</v>
       </c>
     </row>
     <row r="249">
@@ -7907,7 +7907,7 @@
         <v>8</v>
       </c>
       <c r="H249" t="n">
-        <v>0.255527852193518</v>
+        <v>0.2616538410752036</v>
       </c>
     </row>
     <row r="250">
@@ -7937,7 +7937,7 @@
         <v>8</v>
       </c>
       <c r="H250" t="n">
-        <v>0.05795326781135986</v>
+        <v>0.05911887021250927</v>
       </c>
     </row>
     <row r="251">
@@ -7967,7 +7967,7 @@
         <v>1</v>
       </c>
       <c r="H251" t="n">
-        <v>0.07802814719821782</v>
+        <v>0.1068445250690924</v>
       </c>
     </row>
     <row r="252">
@@ -7997,7 +7997,7 @@
         <v>7</v>
       </c>
       <c r="H252" t="n">
-        <v>0.1515304158303124</v>
+        <v>0.1713937987808021</v>
       </c>
     </row>
     <row r="253">
@@ -8027,7 +8027,7 @@
         <v>7</v>
       </c>
       <c r="H253" t="n">
-        <v>0.1070621156788793</v>
+        <v>0.1171419347584072</v>
       </c>
     </row>
     <row r="254">
@@ -8057,7 +8057,7 @@
         <v>1.368421052631579</v>
       </c>
       <c r="H254" t="n">
-        <v>0.4995527044846564</v>
+        <v>0.5747341798246877</v>
       </c>
     </row>
     <row r="255">
@@ -8087,7 +8087,7 @@
         <v>1.526315789473684</v>
       </c>
       <c r="H255" t="n">
-        <v>0.5974396634589909</v>
+        <v>0.6833851244741334</v>
       </c>
     </row>
     <row r="256">
@@ -8117,7 +8117,7 @@
         <v>0.5263157894736842</v>
       </c>
       <c r="H256" t="n">
-        <v>0.0002398562848393857</v>
+        <v>0.0001261545165828201</v>
       </c>
     </row>
     <row r="257">
@@ -8147,7 +8147,7 @@
         <v>1.184210526315789</v>
       </c>
       <c r="H257" t="n">
-        <v>0.6273884714571618</v>
+        <v>0.7158088365024905</v>
       </c>
     </row>
     <row r="258">
@@ -8177,7 +8177,7 @@
         <v>1.210526315789474</v>
       </c>
       <c r="H258" t="n">
-        <v>0.3105620234446401</v>
+        <v>0.2860563622309915</v>
       </c>
     </row>
     <row r="259">
@@ -8207,7 +8207,7 @@
         <v>0.9210526315789472</v>
       </c>
       <c r="H259" t="n">
-        <v>0.3634497840572659</v>
+        <v>0.3501973877925834</v>
       </c>
     </row>
     <row r="260">
@@ -8237,7 +8237,7 @@
         <v>1.921052631578948</v>
       </c>
       <c r="H260" t="n">
-        <v>0.3387884138883021</v>
+        <v>0.3297655313343767</v>
       </c>
     </row>
     <row r="261">
@@ -8267,7 +8267,7 @@
         <v>3.684210526315789</v>
       </c>
       <c r="H261" t="n">
-        <v>0.7912518322216372</v>
+        <v>0.796412931707751</v>
       </c>
     </row>
     <row r="262">
@@ -8297,7 +8297,7 @@
         <v>1.789473684210526</v>
       </c>
       <c r="H262" t="n">
-        <v>0.4521316672135099</v>
+        <v>0.4355463573304074</v>
       </c>
     </row>
     <row r="263">
@@ -8327,7 +8327,7 @@
         <v>3.105263157894737</v>
       </c>
       <c r="H263" t="n">
-        <v>0.4961231960178284</v>
+        <v>0.5069426602278495</v>
       </c>
     </row>
     <row r="264">
@@ -8357,7 +8357,7 @@
         <v>1.342105263157895</v>
       </c>
       <c r="H264" t="n">
-        <v>0.4882354257504528</v>
+        <v>0.5644734547535101</v>
       </c>
     </row>
     <row r="265">
@@ -8387,7 +8387,7 @@
         <v>1.605263157894737</v>
       </c>
       <c r="H265" t="n">
-        <v>0.5919395890709523</v>
+        <v>0.6629822867211076</v>
       </c>
     </row>
     <row r="266">
@@ -8417,7 +8417,7 @@
         <v>2.368421052631579</v>
       </c>
       <c r="H266" t="n">
-        <v>0.5816793488170078</v>
+        <v>0.5446037360809662</v>
       </c>
     </row>
     <row r="267">
@@ -8447,7 +8447,7 @@
         <v>2.210526315789474</v>
       </c>
       <c r="H267" t="n">
-        <v>0.6624922764747462</v>
+        <v>0.7189235134326668</v>
       </c>
     </row>
     <row r="268">
@@ -8477,7 +8477,7 @@
         <v>4.078947368421052</v>
       </c>
       <c r="H268" t="n">
-        <v>0.6121108657965453</v>
+        <v>0.5509094975040583</v>
       </c>
     </row>
     <row r="269">
@@ -8507,7 +8507,7 @@
         <v>1.842105263157895</v>
       </c>
       <c r="H269" t="n">
-        <v>0.4923699337640293</v>
+        <v>0.5290049941640186</v>
       </c>
     </row>
     <row r="270">
@@ -8537,7 +8537,7 @@
         <v>1.131578947368421</v>
       </c>
       <c r="H270" t="n">
-        <v>0.3194295911854356</v>
+        <v>0.3882725632420222</v>
       </c>
     </row>
     <row r="271">
@@ -8567,7 +8567,7 @@
         <v>1.973684210526316</v>
       </c>
       <c r="H271" t="n">
-        <v>0.4014430649558184</v>
+        <v>0.388730302801176</v>
       </c>
     </row>
     <row r="272">
@@ -8597,7 +8597,7 @@
         <v>0.5</v>
       </c>
       <c r="H272" t="n">
-        <v>0.002690129637647688</v>
+        <v>0.001712257786729703</v>
       </c>
     </row>
     <row r="273">
@@ -8627,7 +8627,7 @@
         <v>1.763157894736842</v>
       </c>
       <c r="H273" t="n">
-        <v>0.3306802812931223</v>
+        <v>0.3262789063837255</v>
       </c>
     </row>
     <row r="274">
@@ -8657,7 +8657,7 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="H274" t="n">
-        <v>0.2406716602465525</v>
+        <v>0.1940658953899707</v>
       </c>
     </row>
     <row r="275">
@@ -8687,7 +8687,7 @@
         <v>1.421052631578947</v>
       </c>
       <c r="H275" t="n">
-        <v>0.4530571894379342</v>
+        <v>0.4812264954174714</v>
       </c>
     </row>
     <row r="276">
@@ -8717,7 +8717,7 @@
         <v>2.368421052631579</v>
       </c>
       <c r="H276" t="n">
-        <v>0.3324742921043869</v>
+        <v>0.3957662375298482</v>
       </c>
     </row>
     <row r="277">
@@ -8747,7 +8747,7 @@
         <v>2.710526315789474</v>
       </c>
       <c r="H277" t="n">
-        <v>0.3504625765938148</v>
+        <v>0.3523136198870186</v>
       </c>
     </row>
     <row r="278">
@@ -8777,7 +8777,7 @@
         <v>1.868421052631579</v>
       </c>
       <c r="H278" t="n">
-        <v>0.3568075402187555</v>
+        <v>0.4541902397713646</v>
       </c>
     </row>
     <row r="279">
@@ -8807,7 +8807,7 @@
         <v>3.289473684210526</v>
       </c>
       <c r="H279" t="n">
-        <v>0.4733257055932125</v>
+        <v>0.4800546543439397</v>
       </c>
     </row>
     <row r="280">
@@ -8837,7 +8837,7 @@
         <v>3.947368421052632</v>
       </c>
       <c r="H280" t="n">
-        <v>0.6289942041392215</v>
+        <v>0.6339462829700436</v>
       </c>
     </row>
     <row r="281">
@@ -8867,7 +8867,7 @@
         <v>6.052631578947368</v>
       </c>
       <c r="H281" t="n">
-        <v>0.6457494751266266</v>
+        <v>0.6874956106402431</v>
       </c>
     </row>
     <row r="282">
@@ -8897,7 +8897,7 @@
         <v>20.18421052631579</v>
       </c>
       <c r="H282" t="n">
-        <v>0.6334371194195152</v>
+        <v>0.6268068932321403</v>
       </c>
     </row>
     <row r="283">
@@ -8927,7 +8927,7 @@
         <v>8.973684210526315</v>
       </c>
       <c r="H283" t="n">
-        <v>0.6857346894474043</v>
+        <v>0.6649510064388796</v>
       </c>
     </row>
     <row r="284">
@@ -8957,7 +8957,7 @@
         <v>1.263157894736842</v>
       </c>
       <c r="H284" t="n">
-        <v>0.5328059858647343</v>
+        <v>0.5482344206743085</v>
       </c>
     </row>
     <row r="285">
@@ -8987,7 +8987,7 @@
         <v>8.421052631578947</v>
       </c>
       <c r="H285" t="n">
-        <v>0.4546396799700043</v>
+        <v>0.4979444056491322</v>
       </c>
     </row>
     <row r="286">
@@ -9017,7 +9017,7 @@
         <v>5.763157894736842</v>
       </c>
       <c r="H286" t="n">
-        <v>0.2641721604152677</v>
+        <v>0.1834966043087085</v>
       </c>
     </row>
     <row r="287">
@@ -9047,7 +9047,7 @@
         <v>6.710526315789473</v>
       </c>
       <c r="H287" t="n">
-        <v>0.5649537232389426</v>
+        <v>0.5670391424230853</v>
       </c>
     </row>
     <row r="288">
@@ -9077,7 +9077,7 @@
         <v>1.105263157894737</v>
       </c>
       <c r="H288" t="n">
-        <v>0.1877907902792851</v>
+        <v>0.1796658769294775</v>
       </c>
     </row>
     <row r="289">
@@ -9107,7 +9107,7 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="H289" t="n">
-        <v>0.312695883177955</v>
+        <v>0.2978416790847361</v>
       </c>
     </row>
     <row r="290">
@@ -9137,7 +9137,7 @@
         <v>36.36842105263158</v>
       </c>
       <c r="H290" t="n">
-        <v>0.6899541969511122</v>
+        <v>0.6692533080721362</v>
       </c>
     </row>
     <row r="291">
@@ -9167,7 +9167,7 @@
         <v>9.605263157894736</v>
       </c>
       <c r="H291" t="n">
-        <v>0.723767859863103</v>
+        <v>0.7399322822713945</v>
       </c>
     </row>
     <row r="292">
@@ -9197,7 +9197,7 @@
         <v>7.236842105263157</v>
       </c>
       <c r="H292" t="n">
-        <v>0.4437350473743433</v>
+        <v>0.4134616595030525</v>
       </c>
     </row>
     <row r="293">
@@ -9227,7 +9227,7 @@
         <v>1.315789473684211</v>
       </c>
       <c r="H293" t="n">
-        <v>0.4299610265448605</v>
+        <v>0.4743719027800207</v>
       </c>
     </row>
     <row r="294">
@@ -9257,7 +9257,7 @@
         <v>51.6578947368421</v>
       </c>
       <c r="H294" t="n">
-        <v>0.6089802831894321</v>
+        <v>0.6118754408187161</v>
       </c>
     </row>
     <row r="295">
@@ -9287,7 +9287,7 @@
         <v>1.552631578947368</v>
       </c>
       <c r="H295" t="n">
-        <v>0.08147293157654746</v>
+        <v>0.07074382925467806</v>
       </c>
     </row>
     <row r="296">
@@ -9317,7 +9317,7 @@
         <v>142.7894736842105</v>
       </c>
       <c r="H296" t="n">
-        <v>0.9503724396419455</v>
+        <v>0.9693663767137188</v>
       </c>
     </row>
     <row r="297">
@@ -9347,7 +9347,7 @@
         <v>4.157894736842105</v>
       </c>
       <c r="H297" t="n">
-        <v>0.4307087664585891</v>
+        <v>0.4410974316071024</v>
       </c>
     </row>
     <row r="298">
@@ -9377,7 +9377,7 @@
         <v>7.105263157894737</v>
       </c>
       <c r="H298" t="n">
-        <v>0.2760556523127561</v>
+        <v>0.2973973637784623</v>
       </c>
     </row>
     <row r="299">
@@ -9407,7 +9407,7 @@
         <v>1.052631578947368</v>
       </c>
       <c r="H299" t="n">
-        <v>0.287689447306274</v>
+        <v>0.258053464892349</v>
       </c>
     </row>
     <row r="300">
@@ -9437,7 +9437,7 @@
         <v>4.736842105263158</v>
       </c>
       <c r="H300" t="n">
-        <v>0.2569859290723173</v>
+        <v>0.262017260771672</v>
       </c>
     </row>
     <row r="301">
@@ -9467,7 +9467,7 @@
         <v>160.6052631578947</v>
       </c>
       <c r="H301" t="n">
-        <v>0.9999922860944233</v>
+        <v>0.9999997160307856</v>
       </c>
     </row>
     <row r="302">
@@ -9497,7 +9497,7 @@
         <v>13.3421052631579</v>
       </c>
       <c r="H302" t="n">
-        <v>0.5653767890773131</v>
+        <v>0.5860602249612755</v>
       </c>
     </row>
     <row r="303">
@@ -9527,7 +9527,7 @@
         <v>19.89473684210526</v>
       </c>
       <c r="H303" t="n">
-        <v>0.4104304910563649</v>
+        <v>0.4358079777451295</v>
       </c>
     </row>
     <row r="304">
@@ -9557,7 +9557,7 @@
         <v>24.60526315789474</v>
       </c>
       <c r="H304" t="n">
-        <v>0.4020288738417909</v>
+        <v>0.4345163560251241</v>
       </c>
     </row>
     <row r="305">
@@ -9587,7 +9587,7 @@
         <v>5.394736842105263</v>
       </c>
       <c r="H305" t="n">
-        <v>0.4713455716571023</v>
+        <v>0.4400583183153756</v>
       </c>
     </row>
     <row r="306">
@@ -9617,7 +9617,7 @@
         <v>8.268156424581006</v>
       </c>
       <c r="H306" t="n">
-        <v>0.54157166757582</v>
+        <v>0.5332263100002202</v>
       </c>
     </row>
     <row r="307">
@@ -9647,7 +9647,7 @@
         <v>9.441340782122904</v>
       </c>
       <c r="H307" t="n">
-        <v>0.5548477129176017</v>
+        <v>0.5321793989577807</v>
       </c>
     </row>
     <row r="308">
@@ -9677,7 +9677,7 @@
         <v>25.3072625698324</v>
       </c>
       <c r="H308" t="n">
-        <v>0.9763634120253957</v>
+        <v>0.9888940947202975</v>
       </c>
     </row>
     <row r="309">
@@ -9707,7 +9707,7 @@
         <v>6.703910614525141</v>
       </c>
       <c r="H309" t="n">
-        <v>0.6363230767570767</v>
+        <v>0.693294223061846</v>
       </c>
     </row>
     <row r="310">
@@ -9737,7 +9737,7 @@
         <v>2.905027932960894</v>
       </c>
       <c r="H310" t="n">
-        <v>0.3871882320969088</v>
+        <v>0.3907749624007608</v>
       </c>
     </row>
     <row r="311">
@@ -9767,7 +9767,7 @@
         <v>3.519553072625698</v>
       </c>
       <c r="H311" t="n">
-        <v>0.4265254009023583</v>
+        <v>0.467812192672568</v>
       </c>
     </row>
     <row r="312">
@@ -9797,7 +9797,7 @@
         <v>11.42458100558659</v>
       </c>
       <c r="H312" t="n">
-        <v>0.7118453076057101</v>
+        <v>0.7792425300924765</v>
       </c>
     </row>
     <row r="313">
@@ -9827,7 +9827,7 @@
         <v>82.37430167597766</v>
       </c>
       <c r="H313" t="n">
-        <v>0.8884190476171752</v>
+        <v>0.8623012977683772</v>
       </c>
     </row>
     <row r="314">
@@ -9857,7 +9857,7 @@
         <v>4.050279329608939</v>
       </c>
       <c r="H314" t="n">
-        <v>0.3008112617476119</v>
+        <v>0.2253792899708065</v>
       </c>
     </row>
     <row r="315">
@@ -9887,7 +9887,7 @@
         <v>9.553072625698324</v>
       </c>
       <c r="H315" t="n">
-        <v>0.3814390389192256</v>
+        <v>0.3376174900919385</v>
       </c>
     </row>
     <row r="316">
@@ -9917,7 +9917,7 @@
         <v>7.29050279329609</v>
       </c>
       <c r="H316" t="n">
-        <v>0.4286566294798211</v>
+        <v>0.4447403957147686</v>
       </c>
     </row>
     <row r="317">
@@ -9947,7 +9947,7 @@
         <v>18.77094972067039</v>
       </c>
       <c r="H317" t="n">
-        <v>0.9622585972524423</v>
+        <v>0.982016739077612</v>
       </c>
     </row>
     <row r="318">
@@ -9977,7 +9977,7 @@
         <v>1.983240223463687</v>
       </c>
       <c r="H318" t="n">
-        <v>0.2852379555424717</v>
+        <v>0.227346946864366</v>
       </c>
     </row>
     <row r="319">
@@ -10007,7 +10007,7 @@
         <v>17.93296089385475</v>
       </c>
       <c r="H319" t="n">
-        <v>0.6340088695641152</v>
+        <v>0.6480920597584044</v>
       </c>
     </row>
     <row r="320">
@@ -10037,7 +10037,7 @@
         <v>1</v>
       </c>
       <c r="H320" t="n">
-        <v>0.1021638565492962</v>
+        <v>0.09106506902462033</v>
       </c>
     </row>
     <row r="321">
@@ -10067,7 +10067,7 @@
         <v>2</v>
       </c>
       <c r="H321" t="n">
-        <v>0.4683520093245546</v>
+        <v>0.418298623353254</v>
       </c>
     </row>
     <row r="322">
@@ -10097,7 +10097,7 @@
         <v>11</v>
       </c>
       <c r="H322" t="n">
-        <v>0.2629348734220474</v>
+        <v>0.2577635658275216</v>
       </c>
     </row>
     <row r="323">
@@ -10127,7 +10127,7 @@
         <v>4</v>
       </c>
       <c r="H323" t="n">
-        <v>0.03380457741617005</v>
+        <v>0.02420109909279743</v>
       </c>
     </row>
     <row r="324">
@@ -10157,7 +10157,7 @@
         <v>8</v>
       </c>
       <c r="H324" t="n">
-        <v>0.4938184674286441</v>
+        <v>0.4960484380670571</v>
       </c>
     </row>
     <row r="325">
@@ -10187,7 +10187,7 @@
         <v>38</v>
       </c>
       <c r="H325" t="n">
-        <v>0.7354253186703044</v>
+        <v>0.78105435701962</v>
       </c>
     </row>
     <row r="326">
@@ -10217,7 +10217,7 @@
         <v>6</v>
       </c>
       <c r="H326" t="n">
-        <v>0.0468003422888708</v>
+        <v>0.03146648603235581</v>
       </c>
     </row>
     <row r="327">
@@ -10247,7 +10247,7 @@
         <v>11</v>
       </c>
       <c r="H327" t="n">
-        <v>0.1140260720370754</v>
+        <v>0.08357031213397267</v>
       </c>
     </row>
     <row r="328">
@@ -10277,7 +10277,7 @@
         <v>8</v>
       </c>
       <c r="H328" t="n">
-        <v>0.07614324864376651</v>
+        <v>0.06281519040630987</v>
       </c>
     </row>
     <row r="329">
@@ -10307,7 +10307,7 @@
         <v>6</v>
       </c>
       <c r="H329" t="n">
-        <v>0.05506511424406771</v>
+        <v>0.04458231766442141</v>
       </c>
     </row>
     <row r="330">
@@ -10337,7 +10337,7 @@
         <v>12</v>
       </c>
       <c r="H330" t="n">
-        <v>0.4357145832458678</v>
+        <v>0.4465349627627885</v>
       </c>
     </row>
     <row r="331">
@@ -10367,7 +10367,7 @@
         <v>11</v>
       </c>
       <c r="H331" t="n">
-        <v>0.2304148680716634</v>
+        <v>0.2157886149504182</v>
       </c>
     </row>
     <row r="332">
@@ -10397,7 +10397,7 @@
         <v>5</v>
       </c>
       <c r="H332" t="n">
-        <v>0.09362824179315805</v>
+        <v>0.09154211441241311</v>
       </c>
     </row>
     <row r="333">
@@ -10427,7 +10427,7 @@
         <v>19</v>
       </c>
       <c r="H333" t="n">
-        <v>0.5406693167199362</v>
+        <v>0.551067984757257</v>
       </c>
     </row>
     <row r="334">
@@ -10457,7 +10457,7 @@
         <v>33</v>
       </c>
       <c r="H334" t="n">
-        <v>0.6457085290604841</v>
+        <v>0.6047125216777007</v>
       </c>
     </row>
     <row r="335">
@@ -10487,7 +10487,7 @@
         <v>2</v>
       </c>
       <c r="H335" t="n">
-        <v>0.01805923646733754</v>
+        <v>0.01077668135755987</v>
       </c>
     </row>
     <row r="336">
@@ -10517,7 +10517,7 @@
         <v>14</v>
       </c>
       <c r="H336" t="n">
-        <v>0.6188393891789921</v>
+        <v>0.6110134054085392</v>
       </c>
     </row>
     <row r="337">
@@ -10547,7 +10547,7 @@
         <v>9</v>
       </c>
       <c r="H337" t="n">
-        <v>0.1027501270546483</v>
+        <v>0.07936627485304601</v>
       </c>
     </row>
     <row r="338">
@@ -10577,7 +10577,7 @@
         <v>12</v>
       </c>
       <c r="H338" t="n">
-        <v>0.04479477173499605</v>
+        <v>0.05056650159630621</v>
       </c>
     </row>
     <row r="339">
@@ -10607,7 +10607,7 @@
         <v>6</v>
       </c>
       <c r="H339" t="n">
-        <v>0.1635727902941342</v>
+        <v>0.1417038548205302</v>
       </c>
     </row>
     <row r="340">
@@ -10637,7 +10637,7 @@
         <v>15</v>
       </c>
       <c r="H340" t="n">
-        <v>0.5007779099393207</v>
+        <v>0.4554167137012593</v>
       </c>
     </row>
     <row r="341">
@@ -10667,7 +10667,7 @@
         <v>13</v>
       </c>
       <c r="H341" t="n">
-        <v>0.1220232870946975</v>
+        <v>0.1024303845118884</v>
       </c>
     </row>
     <row r="342">
@@ -10697,7 +10697,7 @@
         <v>7</v>
       </c>
       <c r="H342" t="n">
-        <v>0.4476009873303888</v>
+        <v>0.440190979231053</v>
       </c>
     </row>
     <row r="343">
@@ -10727,7 +10727,7 @@
         <v>6</v>
       </c>
       <c r="H343" t="n">
-        <v>0.2529246304350579</v>
+        <v>0.2738789688910576</v>
       </c>
     </row>
     <row r="344">
@@ -10757,7 +10757,7 @@
         <v>6</v>
       </c>
       <c r="H344" t="n">
-        <v>0.1235842817478207</v>
+        <v>0.1539220452843061</v>
       </c>
     </row>
     <row r="345">
@@ -10787,7 +10787,7 @@
         <v>3</v>
       </c>
       <c r="H345" t="n">
-        <v>0.05701945299101372</v>
+        <v>0.04988352125542721</v>
       </c>
     </row>
     <row r="346">
@@ -10817,7 +10817,7 @@
         <v>8</v>
       </c>
       <c r="H346" t="n">
-        <v>0.07024507014863592</v>
+        <v>0.05483997839638281</v>
       </c>
     </row>
     <row r="347">
@@ -10847,7 +10847,7 @@
         <v>8</v>
       </c>
       <c r="H347" t="n">
-        <v>0.1148837666000022</v>
+        <v>0.1067497792096133</v>
       </c>
     </row>
     <row r="348">
@@ -10877,7 +10877,7 @@
         <v>1</v>
       </c>
       <c r="H348" t="n">
-        <v>0.329694947670805</v>
+        <v>0.3214315970914432</v>
       </c>
     </row>
     <row r="349">
@@ -10907,7 +10907,7 @@
         <v>5</v>
       </c>
       <c r="H349" t="n">
-        <v>0.1541672087243078</v>
+        <v>0.1357773962311051</v>
       </c>
     </row>
     <row r="350">
@@ -10937,7 +10937,7 @@
         <v>14</v>
       </c>
       <c r="H350" t="n">
-        <v>0.1454196489742294</v>
+        <v>0.1350074051188395</v>
       </c>
     </row>
     <row r="351">
@@ -10967,7 +10967,7 @@
         <v>6</v>
       </c>
       <c r="H351" t="n">
-        <v>0.03869373410161869</v>
+        <v>0.03235307187489765</v>
       </c>
     </row>
     <row r="352">
@@ -10997,7 +10997,7 @@
         <v>5</v>
       </c>
       <c r="H352" t="n">
-        <v>0.03804324872255686</v>
+        <v>0.03134374927771548</v>
       </c>
     </row>
     <row r="353">
@@ -11027,7 +11027,7 @@
         <v>8</v>
       </c>
       <c r="H353" t="n">
-        <v>0.09101007411538224</v>
+        <v>0.07710107032715857</v>
       </c>
     </row>
     <row r="354">
@@ -11057,7 +11057,7 @@
         <v>17</v>
       </c>
       <c r="H354" t="n">
-        <v>0.1039122655246252</v>
+        <v>0.07077852485487512</v>
       </c>
     </row>
     <row r="355">
@@ -11087,7 +11087,7 @@
         <v>18</v>
       </c>
       <c r="H355" t="n">
-        <v>0.8703661434900678</v>
+        <v>0.8651082069765903</v>
       </c>
     </row>
     <row r="356">
@@ -11117,7 +11117,7 @@
         <v>5</v>
       </c>
       <c r="H356" t="n">
-        <v>0.05942536997436125</v>
+        <v>0.04008273019676144</v>
       </c>
     </row>
     <row r="357">
@@ -11147,7 +11147,7 @@
         <v>8</v>
       </c>
       <c r="H357" t="n">
-        <v>0.126313550949766</v>
+        <v>0.1781947493877855</v>
       </c>
     </row>
     <row r="358">
@@ -11177,7 +11177,7 @@
         <v>8</v>
       </c>
       <c r="H358" t="n">
-        <v>0.1553262449180286</v>
+        <v>0.1124617574354872</v>
       </c>
     </row>
     <row r="359">
@@ -11207,7 +11207,7 @@
         <v>15</v>
       </c>
       <c r="H359" t="n">
-        <v>0.596471383982344</v>
+        <v>0.6778145753634554</v>
       </c>
     </row>
     <row r="360">
@@ -11237,7 +11237,7 @@
         <v>8</v>
       </c>
       <c r="H360" t="n">
-        <v>0.3847509683249689</v>
+        <v>0.3376810605024129</v>
       </c>
     </row>
     <row r="361">
@@ -11267,7 +11267,7 @@
         <v>15</v>
       </c>
       <c r="H361" t="n">
-        <v>0.1195097048198047</v>
+        <v>0.09348742855444005</v>
       </c>
     </row>
     <row r="362">
@@ -11297,7 +11297,7 @@
         <v>6</v>
       </c>
       <c r="H362" t="n">
-        <v>0.07981914534884418</v>
+        <v>0.08631500095966819</v>
       </c>
     </row>
     <row r="363">
@@ -11327,7 +11327,7 @@
         <v>4</v>
       </c>
       <c r="H363" t="n">
-        <v>0.4254419381056958</v>
+        <v>0.4147640435308065</v>
       </c>
     </row>
     <row r="364">
@@ -11357,7 +11357,7 @@
         <v>5</v>
       </c>
       <c r="H364" t="n">
-        <v>0.1151785036814676</v>
+        <v>0.1447249941661938</v>
       </c>
     </row>
     <row r="365">
@@ -11387,7 +11387,7 @@
         <v>5</v>
       </c>
       <c r="H365" t="n">
-        <v>0.09171172468228563</v>
+        <v>0.06840995396539354</v>
       </c>
     </row>
     <row r="366">
@@ -11417,7 +11417,7 @@
         <v>5</v>
       </c>
       <c r="H366" t="n">
-        <v>0.6931855159064717</v>
+        <v>0.703022061795644</v>
       </c>
     </row>
     <row r="367">
@@ -11447,7 +11447,7 @@
         <v>11</v>
       </c>
       <c r="H367" t="n">
-        <v>0.1680700319995911</v>
+        <v>0.1596852728038952</v>
       </c>
     </row>
     <row r="368">
@@ -11477,7 +11477,7 @@
         <v>14</v>
       </c>
       <c r="H368" t="n">
-        <v>0.4550463769425611</v>
+        <v>0.4971113057610642</v>
       </c>
     </row>
     <row r="369">
@@ -11507,7 +11507,7 @@
         <v>3</v>
       </c>
       <c r="H369" t="n">
-        <v>0.114026753642828</v>
+        <v>0.08310384873127358</v>
       </c>
     </row>
     <row r="370">
@@ -11537,7 +11537,7 @@
         <v>3</v>
       </c>
       <c r="H370" t="n">
-        <v>0.2675539224978083</v>
+        <v>0.2429179955915739</v>
       </c>
     </row>
     <row r="371">
@@ -11567,7 +11567,7 @@
         <v>14</v>
       </c>
       <c r="H371" t="n">
-        <v>0.7739862369384436</v>
+        <v>0.7775476345047977</v>
       </c>
     </row>
     <row r="372">
@@ -11597,7 +11597,7 @@
         <v>5</v>
       </c>
       <c r="H372" t="n">
-        <v>0.4290619075438666</v>
+        <v>0.4303513359190819</v>
       </c>
     </row>
     <row r="373">
@@ -11627,7 +11627,7 @@
         <v>4</v>
       </c>
       <c r="H373" t="n">
-        <v>0.1663716895049487</v>
+        <v>0.206573526221896</v>
       </c>
     </row>
     <row r="374">
@@ -11657,7 +11657,7 @@
         <v>5</v>
       </c>
       <c r="H374" t="n">
-        <v>0.03177332860580676</v>
+        <v>0.02054236661718364</v>
       </c>
     </row>
     <row r="375">
@@ -11687,7 +11687,7 @@
         <v>5</v>
       </c>
       <c r="H375" t="n">
-        <v>0.1106388830325963</v>
+        <v>0.1024421643013443</v>
       </c>
     </row>
     <row r="376">
@@ -11717,7 +11717,7 @@
         <v>8</v>
       </c>
       <c r="H376" t="n">
-        <v>0.05391055244034735</v>
+        <v>0.05775780683670939</v>
       </c>
     </row>
     <row r="377">
@@ -11747,7 +11747,7 @@
         <v>7</v>
       </c>
       <c r="H377" t="n">
-        <v>0.1679141698258441</v>
+        <v>0.1763430360368823</v>
       </c>
     </row>
     <row r="378">
@@ -11777,7 +11777,7 @@
         <v>3</v>
       </c>
       <c r="H378" t="n">
-        <v>0.07022697588747366</v>
+        <v>0.05365670869208308</v>
       </c>
     </row>
     <row r="379">
@@ -11807,7 +11807,7 @@
         <v>9</v>
       </c>
       <c r="H379" t="n">
-        <v>0.1465970738776403</v>
+        <v>0.111709145993653</v>
       </c>
     </row>
     <row r="380">
@@ -11837,7 +11837,7 @@
         <v>0.7368421052631579</v>
       </c>
       <c r="H380" t="n">
-        <v>0.2142577401914947</v>
+        <v>0.1335788840917309</v>
       </c>
     </row>
     <row r="381">
@@ -11867,7 +11867,7 @@
         <v>1.81578947368421</v>
       </c>
       <c r="H381" t="n">
-        <v>0.5431824946808553</v>
+        <v>0.5039125582535828</v>
       </c>
     </row>
     <row r="382">
@@ -11897,7 +11897,7 @@
         <v>7.736842105263157</v>
       </c>
       <c r="H382" t="n">
-        <v>0.8945337710134451</v>
+        <v>0.9338111209056553</v>
       </c>
     </row>
     <row r="383">
@@ -11927,7 +11927,7 @@
         <v>2.289473684210526</v>
       </c>
       <c r="H383" t="n">
-        <v>0.5966606029252549</v>
+        <v>0.5783180123065825</v>
       </c>
     </row>
     <row r="384">
@@ -11957,7 +11957,7 @@
         <v>2</v>
       </c>
       <c r="H384" t="n">
-        <v>0.2417208336914051</v>
+        <v>0.1654671990302191</v>
       </c>
     </row>
     <row r="385">
@@ -11987,7 +11987,7 @@
         <v>1.526315789473684</v>
       </c>
       <c r="H385" t="n">
-        <v>0.54023395593654</v>
+        <v>0.6050789888562401</v>
       </c>
     </row>
     <row r="386">
@@ -12017,7 +12017,7 @@
         <v>1.473684210526316</v>
       </c>
       <c r="H386" t="n">
-        <v>0.4708917790990773</v>
+        <v>0.5039961301170041</v>
       </c>
     </row>
     <row r="387">
@@ -12047,7 +12047,7 @@
         <v>2.105263157894737</v>
       </c>
       <c r="H387" t="n">
-        <v>0.5559194772126951</v>
+        <v>0.5890618430847777</v>
       </c>
     </row>
     <row r="388">
@@ -12077,7 +12077,7 @@
         <v>1.263157894736842</v>
       </c>
       <c r="H388" t="n">
-        <v>0.4056694235335198</v>
+        <v>0.3802104745787609</v>
       </c>
     </row>
     <row r="389">
@@ -12107,7 +12107,7 @@
         <v>0.6842105263157895</v>
       </c>
       <c r="H389" t="n">
-        <v>0.3553663845814184</v>
+        <v>0.518410218703015</v>
       </c>
     </row>
     <row r="390">
@@ -12137,7 +12137,7 @@
         <v>3.473684210526316</v>
       </c>
       <c r="H390" t="n">
-        <v>0.262768194823209</v>
+        <v>0.2288985426162519</v>
       </c>
     </row>
     <row r="391">
@@ -12167,7 +12167,7 @@
         <v>2.763157894736842</v>
       </c>
       <c r="H391" t="n">
-        <v>0.302473703810038</v>
+        <v>0.2951081929408473</v>
       </c>
     </row>
     <row r="392">
@@ -12197,7 +12197,7 @@
         <v>1.552631578947368</v>
       </c>
       <c r="H392" t="n">
-        <v>0.4724161787634363</v>
+        <v>0.4638252931486452</v>
       </c>
     </row>
     <row r="393">
@@ -12227,7 +12227,7 @@
         <v>1.421052631578947</v>
       </c>
       <c r="H393" t="n">
-        <v>0.3505730058078526</v>
+        <v>0.2998999157760664</v>
       </c>
     </row>
     <row r="394">
@@ -12257,7 +12257,7 @@
         <v>1.947368421052632</v>
       </c>
       <c r="H394" t="n">
-        <v>0.2203834445823576</v>
+        <v>0.1847068737093235</v>
       </c>
     </row>
     <row r="395">
@@ -12287,7 +12287,7 @@
         <v>3.5</v>
       </c>
       <c r="H395" t="n">
-        <v>0.401955659150045</v>
+        <v>0.4082739674001356</v>
       </c>
     </row>
     <row r="396">
@@ -12317,7 +12317,7 @@
         <v>1.263157894736842</v>
       </c>
       <c r="H396" t="n">
-        <v>0.3917332047812249</v>
+        <v>0.3932400306464109</v>
       </c>
     </row>
     <row r="397">
@@ -12347,7 +12347,7 @@
         <v>1.736842105263158</v>
       </c>
       <c r="H397" t="n">
-        <v>0.2847660965352325</v>
+        <v>0.3153445869055014</v>
       </c>
     </row>
     <row r="398">
@@ -12377,7 +12377,7 @@
         <v>1.552631578947368</v>
       </c>
       <c r="H398" t="n">
-        <v>0.5151678014392949</v>
+        <v>0.4657550386385434</v>
       </c>
     </row>
     <row r="399">
@@ -12407,7 +12407,7 @@
         <v>2.052631578947369</v>
       </c>
       <c r="H399" t="n">
-        <v>0.3159167656099761</v>
+        <v>0.2405210712576329</v>
       </c>
     </row>
     <row r="400">
@@ -12437,7 +12437,7 @@
         <v>2.394736842105264</v>
       </c>
       <c r="H400" t="n">
-        <v>0.6986769126339776</v>
+        <v>0.7502343078681867</v>
       </c>
     </row>
     <row r="401">
@@ -12467,7 +12467,7 @@
         <v>1.078947368421053</v>
       </c>
       <c r="H401" t="n">
-        <v>0.6267165913747769</v>
+        <v>0.6078563610434713</v>
       </c>
     </row>
     <row r="402">
@@ -12497,7 +12497,7 @@
         <v>2.289473684210526</v>
       </c>
       <c r="H402" t="n">
-        <v>0.6512815859979829</v>
+        <v>0.6279586768741503</v>
       </c>
     </row>
     <row r="403">
@@ -12527,7 +12527,7 @@
         <v>1.973684210526316</v>
       </c>
       <c r="H403" t="n">
-        <v>0.6088943084019971</v>
+        <v>0.6047844713876093</v>
       </c>
     </row>
     <row r="404">
@@ -12557,7 +12557,7 @@
         <v>8.973684210526315</v>
       </c>
       <c r="H404" t="n">
-        <v>0.9222840470566243</v>
+        <v>0.9815322365014719</v>
       </c>
     </row>
     <row r="405">
@@ -12587,7 +12587,7 @@
         <v>2.210526315789474</v>
       </c>
       <c r="H405" t="n">
-        <v>0.2594399731628346</v>
+        <v>0.239588128813762</v>
       </c>
     </row>
     <row r="406">
@@ -12617,7 +12617,7 @@
         <v>2.605263157894737</v>
       </c>
       <c r="H406" t="n">
-        <v>0.1844926256367408</v>
+        <v>0.1757782549983333</v>
       </c>
     </row>
     <row r="407">
@@ -12647,7 +12647,7 @@
         <v>1.868421052631579</v>
       </c>
       <c r="H407" t="n">
-        <v>0.06315945382695251</v>
+        <v>0.04734002711274868</v>
       </c>
     </row>
     <row r="408">
@@ -12677,7 +12677,7 @@
         <v>3.289473684210526</v>
       </c>
       <c r="H408" t="n">
-        <v>0.1517241126624866</v>
+        <v>0.1415189564623777</v>
       </c>
     </row>
     <row r="409">
@@ -12707,7 +12707,7 @@
         <v>6.447368421052632</v>
       </c>
       <c r="H409" t="n">
-        <v>0.6128190155092651</v>
+        <v>0.6801004268790617</v>
       </c>
     </row>
     <row r="410">
@@ -12737,7 +12737,7 @@
         <v>4.157894736842105</v>
       </c>
       <c r="H410" t="n">
-        <v>0.4557357132296426</v>
+        <v>0.4656195538189037</v>
       </c>
     </row>
     <row r="411">
@@ -12767,7 +12767,7 @@
         <v>10.89473684210526</v>
       </c>
       <c r="H411" t="n">
-        <v>0.342334208215378</v>
+        <v>0.3216467198126</v>
       </c>
     </row>
     <row r="412">
@@ -12797,7 +12797,7 @@
         <v>8.184210526315789</v>
       </c>
       <c r="H412" t="n">
-        <v>0.5281043587298062</v>
+        <v>0.5135619894434428</v>
       </c>
     </row>
     <row r="413">
@@ -12827,7 +12827,7 @@
         <v>7.578947368421052</v>
       </c>
       <c r="H413" t="n">
-        <v>0.5129348221596574</v>
+        <v>0.5068445521476789</v>
       </c>
     </row>
     <row r="414">
@@ -12857,7 +12857,7 @@
         <v>60.42105263157895</v>
       </c>
       <c r="H414" t="n">
-        <v>0.3115868543514587</v>
+        <v>0.251067811889031</v>
       </c>
     </row>
     <row r="415">
@@ -12887,7 +12887,7 @@
         <v>17.84210526315789</v>
       </c>
       <c r="H415" t="n">
-        <v>0.8448758683670003</v>
+        <v>0.8638737269380901</v>
       </c>
     </row>
     <row r="416">
@@ -12917,7 +12917,7 @@
         <v>1.894736842105263</v>
       </c>
       <c r="H416" t="n">
-        <v>0.4206501211321366</v>
+        <v>0.4100390525088619</v>
       </c>
     </row>
     <row r="417">
@@ -12947,7 +12947,7 @@
         <v>2.763157894736842</v>
       </c>
       <c r="H417" t="n">
-        <v>0.1955457671212999</v>
+        <v>0.1971631406160716</v>
       </c>
     </row>
     <row r="418">
@@ -12977,7 +12977,7 @@
         <v>3.473684210526316</v>
       </c>
       <c r="H418" t="n">
-        <v>0.3172669669995833</v>
+        <v>0.306952804988589</v>
       </c>
     </row>
     <row r="419">
@@ -13007,7 +13007,7 @@
         <v>1.026315789473684</v>
       </c>
       <c r="H419" t="n">
-        <v>0.3534302724153285</v>
+        <v>0.3776248517177795</v>
       </c>
     </row>
     <row r="420">
@@ -13037,7 +13037,7 @@
         <v>10.10526315789474</v>
       </c>
       <c r="H420" t="n">
-        <v>0.4422965611902832</v>
+        <v>0.4391367122881686</v>
       </c>
     </row>
     <row r="421">
@@ -13067,7 +13067,7 @@
         <v>29.84210526315789</v>
       </c>
       <c r="H421" t="n">
-        <v>0.8008124326920977</v>
+        <v>0.8209835686317801</v>
       </c>
     </row>
     <row r="422">
@@ -13097,7 +13097,7 @@
         <v>2.394736842105264</v>
       </c>
       <c r="H422" t="n">
-        <v>0.3505110888435271</v>
+        <v>0.3541046976967289</v>
       </c>
     </row>
     <row r="423">
@@ -13127,7 +13127,7 @@
         <v>2.078947368421053</v>
       </c>
       <c r="H423" t="n">
-        <v>0.2290960306897906</v>
+        <v>0.1946235212567095</v>
       </c>
     </row>
     <row r="424">
@@ -13157,7 +13157,7 @@
         <v>2.368421052631579</v>
       </c>
       <c r="H424" t="n">
-        <v>0.1436658972422331</v>
+        <v>0.1196191219785134</v>
       </c>
     </row>
     <row r="425">
@@ -13187,7 +13187,7 @@
         <v>19.07894736842105</v>
       </c>
       <c r="H425" t="n">
-        <v>0.5250163871000176</v>
+        <v>0.5199312613681404</v>
       </c>
     </row>
     <row r="426">
@@ -13217,7 +13217,7 @@
         <v>2.421052631578948</v>
       </c>
       <c r="H426" t="n">
-        <v>0.580743344849755</v>
+        <v>0.6277491233688055</v>
       </c>
     </row>
     <row r="427">
@@ -13247,7 +13247,7 @@
         <v>2.289473684210526</v>
       </c>
       <c r="H427" t="n">
-        <v>0.5246028498872159</v>
+        <v>0.5390000504329988</v>
       </c>
     </row>
     <row r="428">
@@ -13277,7 +13277,7 @@
         <v>17.15789473684211</v>
       </c>
       <c r="H428" t="n">
-        <v>0.7877784734977564</v>
+        <v>0.8588005980349995</v>
       </c>
     </row>
     <row r="429">
@@ -13307,7 +13307,7 @@
         <v>7.052631578947368</v>
       </c>
       <c r="H429" t="n">
-        <v>0.0158439940953335</v>
+        <v>0.008630391235885455</v>
       </c>
     </row>
     <row r="430">
@@ -13337,7 +13337,7 @@
         <v>7.947368421052632</v>
       </c>
       <c r="H430" t="n">
-        <v>0.578619848023041</v>
+        <v>0.603941629945818</v>
       </c>
     </row>
     <row r="431">
@@ -13367,7 +13367,7 @@
         <v>1.312849162011173</v>
       </c>
       <c r="H431" t="n">
-        <v>0.4254718607557615</v>
+        <v>0.4609073681562377</v>
       </c>
     </row>
     <row r="432">
@@ -13397,7 +13397,7 @@
         <v>11.11731843575419</v>
       </c>
       <c r="H432" t="n">
-        <v>0.7682838720822227</v>
+        <v>0.8360443763113808</v>
       </c>
     </row>
     <row r="433">
@@ -13427,7 +13427,7 @@
         <v>2.122905027932961</v>
       </c>
       <c r="H433" t="n">
-        <v>0.2504779665374079</v>
+        <v>0.2166398535428734</v>
       </c>
     </row>
     <row r="434">
@@ -13457,7 +13457,7 @@
         <v>5.251396648044693</v>
       </c>
       <c r="H434" t="n">
-        <v>0.379555951292377</v>
+        <v>0.3626128092354146</v>
       </c>
     </row>
     <row r="435">
@@ -13487,7 +13487,7 @@
         <v>14.6927374301676</v>
       </c>
       <c r="H435" t="n">
-        <v>0.8239538406265189</v>
+        <v>0.8472269992034157</v>
       </c>
     </row>
     <row r="436">
@@ -13517,7 +13517,7 @@
         <v>13.10055865921788</v>
       </c>
       <c r="H436" t="n">
-        <v>0.8686141006326584</v>
+        <v>0.9242936161534625</v>
       </c>
     </row>
     <row r="437">
@@ -13547,7 +13547,7 @@
         <v>10.97765363128492</v>
       </c>
       <c r="H437" t="n">
-        <v>0.6176942081285681</v>
+        <v>0.6655309774496341</v>
       </c>
     </row>
     <row r="438">
@@ -13577,7 +13577,7 @@
         <v>11.89944134078212</v>
       </c>
       <c r="H438" t="n">
-        <v>0.9104200883018262</v>
+        <v>0.9493009356932733</v>
       </c>
     </row>
     <row r="439">
@@ -13607,7 +13607,7 @@
         <v>9.022346368715084</v>
       </c>
       <c r="H439" t="n">
-        <v>0.6401000659715489</v>
+        <v>0.7201314155293692</v>
       </c>
     </row>
     <row r="440">
@@ -13637,7 +13637,7 @@
         <v>17.59776536312849</v>
       </c>
       <c r="H440" t="n">
-        <v>0.9583558573508747</v>
+        <v>0.9823079651027025</v>
       </c>
     </row>
     <row r="441">
@@ -13667,7 +13667,7 @@
         <v>6.089385474860336</v>
       </c>
       <c r="H441" t="n">
-        <v>0.8194085167792562</v>
+        <v>0.8666862820581477</v>
       </c>
     </row>
     <row r="442">
@@ -13697,7 +13697,7 @@
         <v>10.11173184357542</v>
       </c>
       <c r="H442" t="n">
-        <v>0.6287094612063023</v>
+        <v>0.6657910654008296</v>
       </c>
     </row>
     <row r="443">
@@ -13727,7 +13727,7 @@
         <v>9.608938547486034</v>
       </c>
       <c r="H443" t="n">
-        <v>0.6346009756221092</v>
+        <v>0.6317036253593888</v>
       </c>
     </row>
     <row r="444">
@@ -13757,7 +13757,7 @@
         <v>4.273743016759777</v>
       </c>
       <c r="H444" t="n">
-        <v>0.5552577512395263</v>
+        <v>0.5657392903344198</v>
       </c>
     </row>
     <row r="445">
@@ -13787,7 +13787,7 @@
         <v>4.385474860335196</v>
       </c>
       <c r="H445" t="n">
-        <v>0.3609889033804878</v>
+        <v>0.340174004581818</v>
       </c>
     </row>
     <row r="446">
@@ -13817,7 +13817,7 @@
         <v>7</v>
       </c>
       <c r="H446" t="n">
-        <v>0.1065224612411663</v>
+        <v>0.07250542168409917</v>
       </c>
     </row>
     <row r="447">
@@ -13847,7 +13847,7 @@
         <v>5</v>
       </c>
       <c r="H447" t="n">
-        <v>0.3316146420455999</v>
+        <v>0.3305685566534199</v>
       </c>
     </row>
     <row r="448">
@@ -13877,7 +13877,7 @@
         <v>6</v>
       </c>
       <c r="H448" t="n">
-        <v>0.09743384152782085</v>
+        <v>0.09297589379231613</v>
       </c>
     </row>
     <row r="449">
@@ -13907,7 +13907,7 @@
         <v>5</v>
       </c>
       <c r="H449" t="n">
-        <v>0.04278766402669522</v>
+        <v>0.03618902993802998</v>
       </c>
     </row>
     <row r="450">
@@ -13937,7 +13937,7 @@
         <v>12</v>
       </c>
       <c r="H450" t="n">
-        <v>0.0494986216645736</v>
+        <v>0.04853869576961878</v>
       </c>
     </row>
     <row r="451">
@@ -13967,7 +13967,7 @@
         <v>22</v>
       </c>
       <c r="H451" t="n">
-        <v>0.1440988868467908</v>
+        <v>0.1189132427437223</v>
       </c>
     </row>
     <row r="452">
@@ -13997,7 +13997,7 @@
         <v>1</v>
       </c>
       <c r="H452" t="n">
-        <v>0.0396646988065727</v>
+        <v>0.03002489700568039</v>
       </c>
     </row>
     <row r="453">
@@ -14027,7 +14027,7 @@
         <v>2</v>
       </c>
       <c r="H453" t="n">
-        <v>0.1464401219931974</v>
+        <v>0.1547103441345297</v>
       </c>
     </row>
     <row r="454">
@@ -14057,7 +14057,7 @@
         <v>23</v>
       </c>
       <c r="H454" t="n">
-        <v>0.6726017806667144</v>
+        <v>0.7148306572637124</v>
       </c>
     </row>
     <row r="455">
@@ -14087,7 +14087,7 @@
         <v>8</v>
       </c>
       <c r="H455" t="n">
-        <v>0.03266920155254618</v>
+        <v>0.03097293697701324</v>
       </c>
     </row>
     <row r="456">
@@ -14117,7 +14117,7 @@
         <v>1</v>
       </c>
       <c r="H456" t="n">
-        <v>0.06405687066009126</v>
+        <v>0.06250773671952152</v>
       </c>
     </row>
     <row r="457">
@@ -14147,7 +14147,7 @@
         <v>6</v>
       </c>
       <c r="H457" t="n">
-        <v>0.1104552619195436</v>
+        <v>0.08063184913843435</v>
       </c>
     </row>
     <row r="458">
@@ -14177,7 +14177,7 @@
         <v>8</v>
       </c>
       <c r="H458" t="n">
-        <v>0.2620208631638729</v>
+        <v>0.337867597310164</v>
       </c>
     </row>
     <row r="459">
@@ -14207,7 +14207,7 @@
         <v>17</v>
       </c>
       <c r="H459" t="n">
-        <v>0.2676265870799536</v>
+        <v>0.2117819949539279</v>
       </c>
     </row>
     <row r="460">
@@ -14237,7 +14237,7 @@
         <v>8</v>
       </c>
       <c r="H460" t="n">
-        <v>0.2789487337298515</v>
+        <v>0.2747505512963559</v>
       </c>
     </row>
     <row r="461">
@@ -14267,7 +14267,7 @@
         <v>8</v>
       </c>
       <c r="H461" t="n">
-        <v>0.3240870271034985</v>
+        <v>0.3572860446603618</v>
       </c>
     </row>
     <row r="462">
@@ -14297,7 +14297,7 @@
         <v>0</v>
       </c>
       <c r="H462" t="n">
-        <v>0.07940283867486406</v>
+        <v>0.06517013316731118</v>
       </c>
     </row>
     <row r="463">
@@ -14327,7 +14327,7 @@
         <v>5</v>
       </c>
       <c r="H463" t="n">
-        <v>0.09470376083387343</v>
+        <v>0.07759520695227591</v>
       </c>
     </row>
     <row r="464">
@@ -14357,7 +14357,7 @@
         <v>59</v>
       </c>
       <c r="H464" t="n">
-        <v>0.8966776952671957</v>
+        <v>0.9061036194811852</v>
       </c>
     </row>
     <row r="465">
@@ -14387,7 +14387,7 @@
         <v>12</v>
       </c>
       <c r="H465" t="n">
-        <v>0.08561534189088091</v>
+        <v>0.07511974129637533</v>
       </c>
     </row>
     <row r="466">
@@ -14417,7 +14417,7 @@
         <v>8</v>
       </c>
       <c r="H466" t="n">
-        <v>0.04084983418604989</v>
+        <v>0.02510890365713405</v>
       </c>
     </row>
     <row r="467">
@@ -14447,7 +14447,7 @@
         <v>14</v>
       </c>
       <c r="H467" t="n">
-        <v>0.6942317755721898</v>
+        <v>0.7870659905971481</v>
       </c>
     </row>
     <row r="468">
@@ -14477,7 +14477,7 @@
         <v>9</v>
       </c>
       <c r="H468" t="n">
-        <v>0.2313629810261774</v>
+        <v>0.215304164780364</v>
       </c>
     </row>
     <row r="469">
@@ -14507,7 +14507,7 @@
         <v>8</v>
       </c>
       <c r="H469" t="n">
-        <v>0.2005684212668228</v>
+        <v>0.2374950273847181</v>
       </c>
     </row>
     <row r="470">
@@ -14537,7 +14537,7 @@
         <v>5</v>
       </c>
       <c r="H470" t="n">
-        <v>0.134940680878836</v>
+        <v>0.1705626141465805</v>
       </c>
     </row>
     <row r="471">
@@ -14567,7 +14567,7 @@
         <v>8</v>
       </c>
       <c r="H471" t="n">
-        <v>0.0326798847747705</v>
+        <v>0.02131929824183822</v>
       </c>
     </row>
     <row r="472">
@@ -14597,7 +14597,7 @@
         <v>7</v>
       </c>
       <c r="H472" t="n">
-        <v>0.03611255021099131</v>
+        <v>0.02477447328510468</v>
       </c>
     </row>
     <row r="473">
@@ -14627,7 +14627,7 @@
         <v>5</v>
       </c>
       <c r="H473" t="n">
-        <v>0.02643000542373376</v>
+        <v>0.02268511912290899</v>
       </c>
     </row>
     <row r="474">
@@ -14657,7 +14657,7 @@
         <v>4</v>
       </c>
       <c r="H474" t="n">
-        <v>0.06899559264226093</v>
+        <v>0.0671266676424921</v>
       </c>
     </row>
     <row r="475">
@@ -14687,7 +14687,7 @@
         <v>8</v>
       </c>
       <c r="H475" t="n">
-        <v>0.198572305391879</v>
+        <v>0.1697078988171537</v>
       </c>
     </row>
     <row r="476">
@@ -14717,7 +14717,7 @@
         <v>8</v>
       </c>
       <c r="H476" t="n">
-        <v>0.08003997705094826</v>
+        <v>0.07211811794249755</v>
       </c>
     </row>
     <row r="477">
@@ -14747,7 +14747,7 @@
         <v>13</v>
       </c>
       <c r="H477" t="n">
-        <v>0.303852139877668</v>
+        <v>0.3564214249136429</v>
       </c>
     </row>
     <row r="478">
@@ -14777,7 +14777,7 @@
         <v>7</v>
       </c>
       <c r="H478" t="n">
-        <v>0.2089001347227398</v>
+        <v>0.1907256918044823</v>
       </c>
     </row>
     <row r="479">
@@ -14807,7 +14807,7 @@
         <v>12</v>
       </c>
       <c r="H479" t="n">
-        <v>0.4464250005124235</v>
+        <v>0.5048774854037937</v>
       </c>
     </row>
     <row r="480">
@@ -14837,7 +14837,7 @@
         <v>10</v>
       </c>
       <c r="H480" t="n">
-        <v>0.2086569530977858</v>
+        <v>0.2300346139140755</v>
       </c>
     </row>
     <row r="481">
@@ -14867,7 +14867,7 @@
         <v>8</v>
       </c>
       <c r="H481" t="n">
-        <v>0.1536183509719123</v>
+        <v>0.1514590826329283</v>
       </c>
     </row>
     <row r="482">
@@ -14897,7 +14897,7 @@
         <v>8</v>
       </c>
       <c r="H482" t="n">
-        <v>0.2549190623743491</v>
+        <v>0.3447141261956264</v>
       </c>
     </row>
     <row r="483">
@@ -14927,7 +14927,7 @@
         <v>14</v>
       </c>
       <c r="H483" t="n">
-        <v>0.5513923798628525</v>
+        <v>0.6523448395078038</v>
       </c>
     </row>
     <row r="484">
@@ -14957,7 +14957,7 @@
         <v>7</v>
       </c>
       <c r="H484" t="n">
-        <v>0.04643792428415876</v>
+        <v>0.04486990578300482</v>
       </c>
     </row>
     <row r="485">
@@ -14987,7 +14987,7 @@
         <v>19</v>
       </c>
       <c r="H485" t="n">
-        <v>0.2580728076495583</v>
+        <v>0.2249725257870544</v>
       </c>
     </row>
     <row r="486">
@@ -15017,7 +15017,7 @@
         <v>8</v>
       </c>
       <c r="H486" t="n">
-        <v>0.07782205710018479</v>
+        <v>0.04541477186023207</v>
       </c>
     </row>
     <row r="487">
@@ -15047,7 +15047,7 @@
         <v>10</v>
       </c>
       <c r="H487" t="n">
-        <v>0.207382877707925</v>
+        <v>0.1942264330954635</v>
       </c>
     </row>
     <row r="488">
@@ -15077,7 +15077,7 @@
         <v>3</v>
       </c>
       <c r="H488" t="n">
-        <v>0.1305291304501823</v>
+        <v>0.1256015957366283</v>
       </c>
     </row>
     <row r="489">
@@ -15107,7 +15107,7 @@
         <v>10</v>
       </c>
       <c r="H489" t="n">
-        <v>0.09992924734054319</v>
+        <v>0.0792700789946284</v>
       </c>
     </row>
     <row r="490">
@@ -15137,7 +15137,7 @@
         <v>8</v>
       </c>
       <c r="H490" t="n">
-        <v>0.1683775209547927</v>
+        <v>0.1276888029306186</v>
       </c>
     </row>
     <row r="491">
@@ -15167,7 +15167,7 @@
         <v>8</v>
       </c>
       <c r="H491" t="n">
-        <v>0.1403233533568277</v>
+        <v>0.1850210731183417</v>
       </c>
     </row>
     <row r="492">
@@ -15197,7 +15197,7 @@
         <v>26</v>
       </c>
       <c r="H492" t="n">
-        <v>0.4415599727387859</v>
+        <v>0.4728169126028118</v>
       </c>
     </row>
     <row r="493">
@@ -15227,7 +15227,7 @@
         <v>62</v>
       </c>
       <c r="H493" t="n">
-        <v>0.9836257707727057</v>
+        <v>0.984901903922286</v>
       </c>
     </row>
     <row r="494">
@@ -15257,7 +15257,7 @@
         <v>8</v>
       </c>
       <c r="H494" t="n">
-        <v>0.2345333912245206</v>
+        <v>0.2243258915601186</v>
       </c>
     </row>
     <row r="495">
@@ -15287,7 +15287,7 @@
         <v>8</v>
       </c>
       <c r="H495" t="n">
-        <v>0.04279938373903862</v>
+        <v>0.03325664005711865</v>
       </c>
     </row>
     <row r="496">
@@ -15317,7 +15317,7 @@
         <v>8</v>
       </c>
       <c r="H496" t="n">
-        <v>0.07232525615020202</v>
+        <v>0.0822335526067214</v>
       </c>
     </row>
     <row r="497">
@@ -15347,7 +15347,7 @@
         <v>19</v>
       </c>
       <c r="H497" t="n">
-        <v>0.3185012499583582</v>
+        <v>0.3269728244054547</v>
       </c>
     </row>
     <row r="498">
@@ -15377,7 +15377,7 @@
         <v>2</v>
       </c>
       <c r="H498" t="n">
-        <v>0.02536928126907398</v>
+        <v>0.0183874772918227</v>
       </c>
     </row>
     <row r="499">
@@ -15407,7 +15407,7 @@
         <v>8</v>
       </c>
       <c r="H499" t="n">
-        <v>0.4823695159990981</v>
+        <v>0.4817610357541719</v>
       </c>
     </row>
     <row r="500">
@@ -15437,7 +15437,7 @@
         <v>6</v>
       </c>
       <c r="H500" t="n">
-        <v>0.275989022467235</v>
+        <v>0.2966320805485806</v>
       </c>
     </row>
     <row r="501">
@@ -15467,7 +15467,7 @@
         <v>7</v>
       </c>
       <c r="H501" t="n">
-        <v>0.04345161699453672</v>
+        <v>0.03005669196918216</v>
       </c>
     </row>
     <row r="502">
@@ -15497,7 +15497,7 @@
         <v>2</v>
       </c>
       <c r="H502" t="n">
-        <v>0.07906401589580186</v>
+        <v>0.0678978054781955</v>
       </c>
     </row>
     <row r="503">
@@ -15527,7 +15527,7 @@
         <v>8</v>
       </c>
       <c r="H503" t="n">
-        <v>0.05105123060568033</v>
+        <v>0.05566873023586185</v>
       </c>
     </row>
     <row r="504">
@@ -15557,7 +15557,7 @@
         <v>8</v>
       </c>
       <c r="H504" t="n">
-        <v>0.2642963493070549</v>
+        <v>0.2543341387994298</v>
       </c>
     </row>
     <row r="505">
@@ -15587,7 +15587,7 @@
         <v>1.657894736842105</v>
       </c>
       <c r="H505" t="n">
-        <v>0.3438601018893182</v>
+        <v>0.371913939370155</v>
       </c>
     </row>
     <row r="506">
@@ -15617,7 +15617,7 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="H506" t="n">
-        <v>0.5191642951804525</v>
+        <v>0.691755549744245</v>
       </c>
     </row>
     <row r="507">
@@ -15647,7 +15647,7 @@
         <v>0.8947368421052632</v>
       </c>
       <c r="H507" t="n">
-        <v>0.7844775993452874</v>
+        <v>0.8198745243125096</v>
       </c>
     </row>
     <row r="508">
@@ -15677,7 +15677,7 @@
         <v>2</v>
       </c>
       <c r="H508" t="n">
-        <v>0.600179144357788</v>
+        <v>0.5304307955617054</v>
       </c>
     </row>
     <row r="509">
@@ -15707,7 +15707,7 @@
         <v>1.763157894736842</v>
       </c>
       <c r="H509" t="n">
-        <v>0.4018785704900715</v>
+        <v>0.3600017590155245</v>
       </c>
     </row>
     <row r="510">
@@ -15737,7 +15737,7 @@
         <v>1.81578947368421</v>
       </c>
       <c r="H510" t="n">
-        <v>0.3851197352261332</v>
+        <v>0.3738532307491715</v>
       </c>
     </row>
     <row r="511">
@@ -15767,7 +15767,7 @@
         <v>1.236842105263158</v>
       </c>
       <c r="H511" t="n">
-        <v>0.7898479037457009</v>
+        <v>0.8214309356787302</v>
       </c>
     </row>
     <row r="512">
@@ -15797,7 +15797,7 @@
         <v>1.210526315789474</v>
       </c>
       <c r="H512" t="n">
-        <v>0.20722850240101</v>
+        <v>0.1560729188347009</v>
       </c>
     </row>
     <row r="513">
@@ -15827,7 +15827,7 @@
         <v>1.421052631578947</v>
       </c>
       <c r="H513" t="n">
-        <v>0.2321086435738102</v>
+        <v>0.3164164455687747</v>
       </c>
     </row>
     <row r="514">
@@ -15857,7 +15857,7 @@
         <v>2.710526315789474</v>
       </c>
       <c r="H514" t="n">
-        <v>0.7728192782391347</v>
+        <v>0.7589596620413136</v>
       </c>
     </row>
     <row r="515">
@@ -15887,7 +15887,7 @@
         <v>0.7631578947368421</v>
       </c>
       <c r="H515" t="n">
-        <v>0.4082446807936972</v>
+        <v>0.3385151920521343</v>
       </c>
     </row>
     <row r="516">
@@ -15917,7 +15917,7 @@
         <v>3.447368421052631</v>
       </c>
       <c r="H516" t="n">
-        <v>0.6215823339800151</v>
+        <v>0.6160869499132255</v>
       </c>
     </row>
     <row r="517">
@@ -15947,7 +15947,7 @@
         <v>0.5</v>
       </c>
       <c r="H517" t="n">
-        <v>0.3677786957004529</v>
+        <v>0.3373862173553346</v>
       </c>
     </row>
     <row r="518">
@@ -15977,7 +15977,7 @@
         <v>1.842105263157895</v>
       </c>
       <c r="H518" t="n">
-        <v>0.2834204762722441</v>
+        <v>0.2556088825155907</v>
       </c>
     </row>
     <row r="519">
@@ -16007,7 +16007,7 @@
         <v>1.473684210526316</v>
       </c>
       <c r="H519" t="n">
-        <v>0.4360134446331881</v>
+        <v>0.4360372483553371</v>
       </c>
     </row>
     <row r="520">
@@ -16037,7 +16037,7 @@
         <v>2.473684210526316</v>
       </c>
       <c r="H520" t="n">
-        <v>0.3590705150518255</v>
+        <v>0.3642063148745602</v>
       </c>
     </row>
     <row r="521">
@@ -16067,7 +16067,7 @@
         <v>2.157894736842105</v>
       </c>
       <c r="H521" t="n">
-        <v>0.5766182572129706</v>
+        <v>0.6280490248201787</v>
       </c>
     </row>
     <row r="522">
@@ -16097,7 +16097,7 @@
         <v>1</v>
       </c>
       <c r="H522" t="n">
-        <v>0.4868663804790245</v>
+        <v>0.5451383894958424</v>
       </c>
     </row>
     <row r="523">
@@ -16127,7 +16127,7 @@
         <v>1.289473684210526</v>
       </c>
       <c r="H523" t="n">
-        <v>0.204599776824488</v>
+        <v>0.1637500184229509</v>
       </c>
     </row>
     <row r="524">
@@ -16157,7 +16157,7 @@
         <v>4.5</v>
       </c>
       <c r="H524" t="n">
-        <v>0.3844688416262755</v>
+        <v>0.3262993622611469</v>
       </c>
     </row>
     <row r="525">
@@ -16187,7 +16187,7 @@
         <v>1.421052631578947</v>
       </c>
       <c r="H525" t="n">
-        <v>0.5858688720826439</v>
+        <v>0.5254069644161503</v>
       </c>
     </row>
     <row r="526">
@@ -16217,7 +16217,7 @@
         <v>6.763157894736842</v>
       </c>
       <c r="H526" t="n">
-        <v>0.6462896193140443</v>
+        <v>0.6405665190478791</v>
       </c>
     </row>
     <row r="527">
@@ -16247,7 +16247,7 @@
         <v>4.763157894736842</v>
       </c>
       <c r="H527" t="n">
-        <v>0.5426810985451743</v>
+        <v>0.4519505253171244</v>
       </c>
     </row>
     <row r="528">
@@ -16277,7 +16277,7 @@
         <v>1.868421052631579</v>
       </c>
       <c r="H528" t="n">
-        <v>0.3834235790846287</v>
+        <v>0.3483982060751256</v>
       </c>
     </row>
     <row r="529">
@@ -16307,7 +16307,7 @@
         <v>1.157894736842105</v>
       </c>
       <c r="H529" t="n">
-        <v>0.3574904585338837</v>
+        <v>0.3499026195406412</v>
       </c>
     </row>
     <row r="530">
@@ -16337,7 +16337,7 @@
         <v>2.631578947368421</v>
       </c>
       <c r="H530" t="n">
-        <v>0.2493774297449033</v>
+        <v>0.2219119118853662</v>
       </c>
     </row>
     <row r="531">
@@ -16367,7 +16367,7 @@
         <v>2.289473684210526</v>
       </c>
       <c r="H531" t="n">
-        <v>0.4662005433714148</v>
+        <v>0.4605224564307139</v>
       </c>
     </row>
     <row r="532">
@@ -16397,7 +16397,7 @@
         <v>3.315789473684211</v>
       </c>
       <c r="H532" t="n">
-        <v>0.7760349672962683</v>
+        <v>0.7933409634826017</v>
       </c>
     </row>
     <row r="533">
@@ -16427,7 +16427,7 @@
         <v>4.526315789473684</v>
       </c>
       <c r="H533" t="n">
-        <v>0.2239195652245341</v>
+        <v>0.2077502077599158</v>
       </c>
     </row>
     <row r="534">
@@ -16457,7 +16457,7 @@
         <v>0.8947368421052632</v>
       </c>
       <c r="H534" t="n">
-        <v>0.4744603362843631</v>
+        <v>0.4968654338403147</v>
       </c>
     </row>
     <row r="535">
@@ -16487,7 +16487,7 @@
         <v>1.5</v>
       </c>
       <c r="H535" t="n">
-        <v>0.9274997966818306</v>
+        <v>0.9465300159968481</v>
       </c>
     </row>
     <row r="536">
@@ -16517,7 +16517,7 @@
         <v>7.394736842105263</v>
       </c>
       <c r="H536" t="n">
-        <v>0.6457819095331807</v>
+        <v>0.6545214107834325</v>
       </c>
     </row>
     <row r="537">
@@ -16547,7 +16547,7 @@
         <v>16.57894736842105</v>
       </c>
       <c r="H537" t="n">
-        <v>0.9250000898775836</v>
+        <v>0.9439233784328825</v>
       </c>
     </row>
     <row r="538">
@@ -16577,7 +16577,7 @@
         <v>10.21052631578947</v>
       </c>
       <c r="H538" t="n">
-        <v>0.6755367091645981</v>
+        <v>0.6858811029816935</v>
       </c>
     </row>
     <row r="539">
@@ -16607,7 +16607,7 @@
         <v>22.63157894736842</v>
       </c>
       <c r="H539" t="n">
-        <v>0.7412206675372224</v>
+        <v>0.7587248753748284</v>
       </c>
     </row>
     <row r="540">
@@ -16637,7 +16637,7 @@
         <v>8.789473684210526</v>
       </c>
       <c r="H540" t="n">
-        <v>0.7702292052447864</v>
+        <v>0.8134061327606584</v>
       </c>
     </row>
     <row r="541">
@@ -16667,7 +16667,7 @@
         <v>9.868421052631581</v>
       </c>
       <c r="H541" t="n">
-        <v>0.2545117768412457</v>
+        <v>0.2348082106514979</v>
       </c>
     </row>
     <row r="542">
@@ -16697,7 +16697,7 @@
         <v>1.210526315789474</v>
       </c>
       <c r="H542" t="n">
-        <v>0.115344608554506</v>
+        <v>0.08951831804374182</v>
       </c>
     </row>
     <row r="543">
@@ -16727,7 +16727,7 @@
         <v>16.86842105263158</v>
       </c>
       <c r="H543" t="n">
-        <v>0.2898070783875118</v>
+        <v>0.2591174326063574</v>
       </c>
     </row>
     <row r="544">
@@ -16757,7 +16757,7 @@
         <v>1.473684210526316</v>
       </c>
       <c r="H544" t="n">
-        <v>0.5855119608891912</v>
+        <v>0.5820642384225052</v>
       </c>
     </row>
     <row r="545">
@@ -16787,7 +16787,7 @@
         <v>12.57894736842105</v>
       </c>
       <c r="H545" t="n">
-        <v>0.3789759385079557</v>
+        <v>0.3781352727404182</v>
       </c>
     </row>
     <row r="546">
@@ -16817,7 +16817,7 @@
         <v>8.605263157894736</v>
       </c>
       <c r="H546" t="n">
-        <v>0.5709920935802325</v>
+        <v>0.5440607975723649</v>
       </c>
     </row>
     <row r="547">
@@ -16847,7 +16847,7 @@
         <v>0.5789473684210527</v>
       </c>
       <c r="H547" t="n">
-        <v>0.06055012013479364</v>
+        <v>0.04209937884368222</v>
       </c>
     </row>
     <row r="548">
@@ -16877,7 +16877,7 @@
         <v>45.63157894736842</v>
       </c>
       <c r="H548" t="n">
-        <v>0.2665450322060312</v>
+        <v>0.2484510759219756</v>
       </c>
     </row>
     <row r="549">
@@ -16907,7 +16907,7 @@
         <v>10.36842105263158</v>
       </c>
       <c r="H549" t="n">
-        <v>0.6770625416703838</v>
+        <v>0.6816136385902458</v>
       </c>
     </row>
     <row r="550">
@@ -16937,7 +16937,7 @@
         <v>1.052631578947368</v>
       </c>
       <c r="H550" t="n">
-        <v>0.7755753712565197</v>
+        <v>0.8022457348307555</v>
       </c>
     </row>
     <row r="551">
@@ -16967,7 +16967,7 @@
         <v>1.131578947368421</v>
       </c>
       <c r="H551" t="n">
-        <v>0.4191544406466812</v>
+        <v>0.4099605916719586</v>
       </c>
     </row>
     <row r="552">
@@ -16997,7 +16997,7 @@
         <v>5.105263157894737</v>
       </c>
       <c r="H552" t="n">
-        <v>0.2929910873587305</v>
+        <v>0.2871784272957278</v>
       </c>
     </row>
     <row r="553">
@@ -17027,7 +17027,7 @@
         <v>38.86842105263158</v>
       </c>
       <c r="H553" t="n">
-        <v>0.3143874400158119</v>
+        <v>0.2835954385854476</v>
       </c>
     </row>
     <row r="554">
@@ -17057,7 +17057,7 @@
         <v>5.105263157894737</v>
       </c>
       <c r="H554" t="n">
-        <v>0.164190939040306</v>
+        <v>0.1418863817728104</v>
       </c>
     </row>
     <row r="555">
@@ -17087,7 +17087,7 @@
         <v>23.92105263157895</v>
       </c>
       <c r="H555" t="n">
-        <v>0.7452067947806855</v>
+        <v>0.7733415772505969</v>
       </c>
     </row>
     <row r="556">
@@ -17117,7 +17117,7 @@
         <v>4.162011173184358</v>
       </c>
       <c r="H556" t="n">
-        <v>0.3681635327331404</v>
+        <v>0.4093408207591827</v>
       </c>
     </row>
     <row r="557">
@@ -17147,7 +17147,7 @@
         <v>16.81564245810056</v>
       </c>
       <c r="H557" t="n">
-        <v>0.7359305750587163</v>
+        <v>0.7463113691695094</v>
       </c>
     </row>
     <row r="558">
@@ -17177,7 +17177,7 @@
         <v>2.346368715083799</v>
       </c>
       <c r="H558" t="n">
-        <v>0.5461400544689392</v>
+        <v>0.5581942454491741</v>
       </c>
     </row>
     <row r="559">
@@ -17207,7 +17207,7 @@
         <v>21.4804469273743</v>
       </c>
       <c r="H559" t="n">
-        <v>0.9984516557981533</v>
+        <v>0.999063947231009</v>
       </c>
     </row>
     <row r="560">
@@ -17237,7 +17237,7 @@
         <v>3.743016759776537</v>
       </c>
       <c r="H560" t="n">
-        <v>0.5366760956763182</v>
+        <v>0.4817278990906696</v>
       </c>
     </row>
     <row r="561">
@@ -17267,7 +17267,7 @@
         <v>3.35195530726257</v>
       </c>
       <c r="H561" t="n">
-        <v>0.6517853472302978</v>
+        <v>0.7403886641818124</v>
       </c>
     </row>
     <row r="562">
@@ -17297,7 +17297,7 @@
         <v>15.11173184357542</v>
       </c>
       <c r="H562" t="n">
-        <v>0.4084921221125631</v>
+        <v>0.3297984675343359</v>
       </c>
     </row>
     <row r="563">
@@ -17327,7 +17327,7 @@
         <v>9.301675977653632</v>
       </c>
       <c r="H563" t="n">
-        <v>0.4766456844831139</v>
+        <v>0.4791419483538656</v>
       </c>
     </row>
     <row r="564">
@@ -17357,7 +17357,7 @@
         <v>3.435754189944134</v>
       </c>
       <c r="H564" t="n">
-        <v>0.2013253916217747</v>
+        <v>0.1466748202856784</v>
       </c>
     </row>
     <row r="565">
@@ -17387,7 +17387,7 @@
         <v>62.51396648044693</v>
       </c>
       <c r="H565" t="n">
-        <v>0.9992342300223858</v>
+        <v>0.9998110868853729</v>
       </c>
     </row>
     <row r="566">
@@ -17417,7 +17417,7 @@
         <v>16.731843575419</v>
       </c>
       <c r="H566" t="n">
-        <v>0.7684202335364373</v>
+        <v>0.7512131353556868</v>
       </c>
     </row>
     <row r="567">
@@ -17447,7 +17447,7 @@
         <v>5.335195530726257</v>
       </c>
       <c r="H567" t="n">
-        <v>0.6516035635216939</v>
+        <v>0.7065132851124195</v>
       </c>
     </row>
     <row r="568">
@@ -17477,7 +17477,7 @@
         <v>22.0391061452514</v>
       </c>
       <c r="H568" t="n">
-        <v>0.7609776891282277</v>
+        <v>0.7609199654356803</v>
       </c>
     </row>
     <row r="569">
@@ -17507,7 +17507,7 @@
         <v>22.54189944134079</v>
       </c>
       <c r="H569" t="n">
-        <v>0.9183095037789641</v>
+        <v>0.9522516046029283</v>
       </c>
     </row>
     <row r="570">
@@ -17537,7 +17537,7 @@
         <v>9.441340782122904</v>
       </c>
       <c r="H570" t="n">
-        <v>0.6045799353958237</v>
+        <v>0.6593923169571382</v>
       </c>
     </row>
     <row r="571">
@@ -17567,7 +17567,7 @@
         <v>44</v>
       </c>
       <c r="H571" t="n">
-        <v>0.9755988558346135</v>
+        <v>0.9795381196129606</v>
       </c>
     </row>
     <row r="572">
@@ -17597,7 +17597,7 @@
         <v>6</v>
       </c>
       <c r="H572" t="n">
-        <v>0.1109116496584858</v>
+        <v>0.2186224993862288</v>
       </c>
     </row>
     <row r="573">
@@ -17627,7 +17627,7 @@
         <v>8</v>
       </c>
       <c r="H573" t="n">
-        <v>0.02665998906157293</v>
+        <v>0.04298187568342875</v>
       </c>
     </row>
     <row r="574">
@@ -17657,7 +17657,7 @@
         <v>32</v>
       </c>
       <c r="H574" t="n">
-        <v>0.7938779929980635</v>
+        <v>0.7433615303348632</v>
       </c>
     </row>
     <row r="575">
@@ -17687,7 +17687,7 @@
         <v>15</v>
       </c>
       <c r="H575" t="n">
-        <v>0.2395827860694389</v>
+        <v>0.1713031704920629</v>
       </c>
     </row>
     <row r="576">
@@ -17717,7 +17717,7 @@
         <v>8</v>
       </c>
       <c r="H576" t="n">
-        <v>0.06017726834730055</v>
+        <v>0.0540888984948028</v>
       </c>
     </row>
     <row r="577">
@@ -17747,7 +17747,7 @@
         <v>18</v>
       </c>
       <c r="H577" t="n">
-        <v>0.8127315088851466</v>
+        <v>0.8436815465093617</v>
       </c>
     </row>
     <row r="578">
@@ -17777,7 +17777,7 @@
         <v>7</v>
       </c>
       <c r="H578" t="n">
-        <v>0.1666162236460573</v>
+        <v>0.1821542258858262</v>
       </c>
     </row>
     <row r="579">
@@ -17807,7 +17807,7 @@
         <v>13</v>
       </c>
       <c r="H579" t="n">
-        <v>0.1418426334525029</v>
+        <v>0.1154513354522131</v>
       </c>
     </row>
     <row r="580">
@@ -17837,7 +17837,7 @@
         <v>7</v>
       </c>
       <c r="H580" t="n">
-        <v>0.2812518769206133</v>
+        <v>0.2210347258133205</v>
       </c>
     </row>
     <row r="581">
@@ -17867,7 +17867,7 @@
         <v>5</v>
       </c>
       <c r="H581" t="n">
-        <v>0.2742312763638255</v>
+        <v>0.2523917025484045</v>
       </c>
     </row>
     <row r="582">
@@ -17897,7 +17897,7 @@
         <v>18</v>
       </c>
       <c r="H582" t="n">
-        <v>0.1878082649809675</v>
+        <v>0.3316387259821208</v>
       </c>
     </row>
     <row r="583">
@@ -17927,7 +17927,7 @@
         <v>8</v>
       </c>
       <c r="H583" t="n">
-        <v>0.04290667610990346</v>
+        <v>0.09533138172247985</v>
       </c>
     </row>
     <row r="584">
@@ -17957,7 +17957,7 @@
         <v>44</v>
       </c>
       <c r="H584" t="n">
-        <v>0.9588167364984932</v>
+        <v>0.967274071811265</v>
       </c>
     </row>
     <row r="585">
@@ -17987,7 +17987,7 @@
         <v>11</v>
       </c>
       <c r="H585" t="n">
-        <v>0.6206501155968166</v>
+        <v>0.5433648106788865</v>
       </c>
     </row>
     <row r="586">
@@ -18017,7 +18017,7 @@
         <v>12</v>
       </c>
       <c r="H586" t="n">
-        <v>0.3283802266641315</v>
+        <v>0.2523428671452742</v>
       </c>
     </row>
     <row r="587">
@@ -18047,7 +18047,7 @@
         <v>5</v>
       </c>
       <c r="H587" t="n">
-        <v>0.05601680619105489</v>
+        <v>0.0478333778497991</v>
       </c>
     </row>
     <row r="588">
@@ -18077,7 +18077,7 @@
         <v>8</v>
       </c>
       <c r="H588" t="n">
-        <v>0.2211964295291687</v>
+        <v>0.2183383049780543</v>
       </c>
     </row>
     <row r="589">
@@ -18107,7 +18107,7 @@
         <v>13</v>
       </c>
       <c r="H589" t="n">
-        <v>0.2695051566034258</v>
+        <v>0.1900520369323573</v>
       </c>
     </row>
     <row r="590">
@@ -18137,7 +18137,7 @@
         <v>4</v>
       </c>
       <c r="H590" t="n">
-        <v>0.03402538599968258</v>
+        <v>0.05896915108415756</v>
       </c>
     </row>
     <row r="591">
@@ -18167,7 +18167,7 @@
         <v>5</v>
       </c>
       <c r="H591" t="n">
-        <v>0.02618754300622563</v>
+        <v>0.02239680579128364</v>
       </c>
     </row>
     <row r="592">
@@ -18197,7 +18197,7 @@
         <v>32</v>
       </c>
       <c r="H592" t="n">
-        <v>0.6563946025726145</v>
+        <v>0.5938268021528466</v>
       </c>
     </row>
     <row r="593">
@@ -18227,7 +18227,7 @@
         <v>11</v>
       </c>
       <c r="H593" t="n">
-        <v>0.07259034194270841</v>
+        <v>0.0518241941049427</v>
       </c>
     </row>
     <row r="594">
@@ -18257,7 +18257,7 @@
         <v>13</v>
       </c>
       <c r="H594" t="n">
-        <v>0.3555178502122143</v>
+        <v>0.3818448833783827</v>
       </c>
     </row>
     <row r="595">
@@ -18287,7 +18287,7 @@
         <v>27</v>
       </c>
       <c r="H595" t="n">
-        <v>0.9330774561525194</v>
+        <v>0.9549145791112332</v>
       </c>
     </row>
     <row r="596">
@@ -18317,7 +18317,7 @@
         <v>14</v>
       </c>
       <c r="H596" t="n">
-        <v>0.2640796035714015</v>
+        <v>0.2358261721976041</v>
       </c>
     </row>
     <row r="597">
@@ -18347,7 +18347,7 @@
         <v>8</v>
       </c>
       <c r="H597" t="n">
-        <v>0.1263272101437617</v>
+        <v>0.2987526496118357</v>
       </c>
     </row>
     <row r="598">
@@ -18377,7 +18377,7 @@
         <v>1</v>
       </c>
       <c r="H598" t="n">
-        <v>0.1309547414245334</v>
+        <v>0.3107760220432033</v>
       </c>
     </row>
     <row r="599">
@@ -18407,7 +18407,7 @@
         <v>21</v>
       </c>
       <c r="H599" t="n">
-        <v>0.4706294385820013</v>
+        <v>0.542483832786961</v>
       </c>
     </row>
     <row r="600">
@@ -18437,7 +18437,7 @@
         <v>8</v>
       </c>
       <c r="H600" t="n">
-        <v>0.07306607005795308</v>
+        <v>0.08073004847667611</v>
       </c>
     </row>
     <row r="601">
@@ -18467,7 +18467,7 @@
         <v>11</v>
       </c>
       <c r="H601" t="n">
-        <v>0.06456833235371537</v>
+        <v>0.03545060673930098</v>
       </c>
     </row>
     <row r="602">
@@ -18497,7 +18497,7 @@
         <v>5</v>
       </c>
       <c r="H602" t="n">
-        <v>0.1179166011076498</v>
+        <v>0.102278774379649</v>
       </c>
     </row>
     <row r="603">
@@ -18527,7 +18527,7 @@
         <v>8</v>
       </c>
       <c r="H603" t="n">
-        <v>0.382492431890884</v>
+        <v>0.2862063492502761</v>
       </c>
     </row>
     <row r="604">
@@ -18557,7 +18557,7 @@
         <v>5</v>
       </c>
       <c r="H604" t="n">
-        <v>0.06397009219792703</v>
+        <v>0.04625453128646426</v>
       </c>
     </row>
     <row r="605">
@@ -18587,7 +18587,7 @@
         <v>6</v>
       </c>
       <c r="H605" t="n">
-        <v>0.2070021598803572</v>
+        <v>0.1703732275342497</v>
       </c>
     </row>
     <row r="606">
@@ -18617,7 +18617,7 @@
         <v>8</v>
       </c>
       <c r="H606" t="n">
-        <v>0.2238470527820103</v>
+        <v>0.144332461263397</v>
       </c>
     </row>
     <row r="607">
@@ -18647,7 +18647,7 @@
         <v>8</v>
       </c>
       <c r="H607" t="n">
-        <v>0.389708120193778</v>
+        <v>0.3790909656928745</v>
       </c>
     </row>
     <row r="608">
@@ -18677,7 +18677,7 @@
         <v>3</v>
       </c>
       <c r="H608" t="n">
-        <v>0.04320097177957146</v>
+        <v>0.1065211604607302</v>
       </c>
     </row>
     <row r="609">
@@ -18707,7 +18707,7 @@
         <v>8</v>
       </c>
       <c r="H609" t="n">
-        <v>0.0911744271988901</v>
+        <v>0.1095335342549938</v>
       </c>
     </row>
     <row r="610">
@@ -18737,7 +18737,7 @@
         <v>8</v>
       </c>
       <c r="H610" t="n">
-        <v>0.03500420430007592</v>
+        <v>0.07472302799171279</v>
       </c>
     </row>
     <row r="611">
@@ -18767,7 +18767,7 @@
         <v>4</v>
       </c>
       <c r="H611" t="n">
-        <v>0.1433095353654068</v>
+        <v>0.1700759245778362</v>
       </c>
     </row>
     <row r="612">
@@ -18797,7 +18797,7 @@
         <v>8</v>
       </c>
       <c r="H612" t="n">
-        <v>0.03056248682260248</v>
+        <v>0.06710855580210745</v>
       </c>
     </row>
     <row r="613">
@@ -18827,7 +18827,7 @@
         <v>5</v>
       </c>
       <c r="H613" t="n">
-        <v>0.2184760606311337</v>
+        <v>0.1949650350073477</v>
       </c>
     </row>
     <row r="614">
@@ -18857,7 +18857,7 @@
         <v>16</v>
       </c>
       <c r="H614" t="n">
-        <v>0.4996837298910023</v>
+        <v>0.5230314199631233</v>
       </c>
     </row>
     <row r="615">
@@ -18887,7 +18887,7 @@
         <v>20</v>
       </c>
       <c r="H615" t="n">
-        <v>0.7179044917249715</v>
+        <v>0.7986755292144826</v>
       </c>
     </row>
     <row r="616">
@@ -18917,7 +18917,7 @@
         <v>6</v>
       </c>
       <c r="H616" t="n">
-        <v>0.0136316918141953</v>
+        <v>0.006846435674668976</v>
       </c>
     </row>
     <row r="617">
@@ -18947,7 +18947,7 @@
         <v>3</v>
       </c>
       <c r="H617" t="n">
-        <v>0.03566304366719431</v>
+        <v>0.0204858840258934</v>
       </c>
     </row>
     <row r="618">
@@ -18977,7 +18977,7 @@
         <v>5</v>
       </c>
       <c r="H618" t="n">
-        <v>0.1675078068901778</v>
+        <v>0.1111957589602874</v>
       </c>
     </row>
     <row r="619">
@@ -19007,7 +19007,7 @@
         <v>8</v>
       </c>
       <c r="H619" t="n">
-        <v>0.2244919170876672</v>
+        <v>0.2261550626962401</v>
       </c>
     </row>
     <row r="620">
@@ -19037,7 +19037,7 @@
         <v>4</v>
       </c>
       <c r="H620" t="n">
-        <v>0.100738959938089</v>
+        <v>0.05614653156150163</v>
       </c>
     </row>
     <row r="621">
@@ -19067,7 +19067,7 @@
         <v>7</v>
       </c>
       <c r="H621" t="n">
-        <v>0.596570219273359</v>
+        <v>0.6218779642924352</v>
       </c>
     </row>
     <row r="622">
@@ -19097,7 +19097,7 @@
         <v>8</v>
       </c>
       <c r="H622" t="n">
-        <v>0.06065144965001131</v>
+        <v>0.06480038779116157</v>
       </c>
     </row>
     <row r="623">
@@ -19127,7 +19127,7 @@
         <v>24</v>
       </c>
       <c r="H623" t="n">
-        <v>0.385075120650935</v>
+        <v>0.3734511104321473</v>
       </c>
     </row>
     <row r="624">
@@ -19157,7 +19157,7 @@
         <v>5</v>
       </c>
       <c r="H624" t="n">
-        <v>0.05758065267267048</v>
+        <v>0.04920948599350511</v>
       </c>
     </row>
     <row r="625">
@@ -19187,7 +19187,7 @@
         <v>1</v>
       </c>
       <c r="H625" t="n">
-        <v>0.04093574025813948</v>
+        <v>0.03814664944987772</v>
       </c>
     </row>
     <row r="626">
@@ -19217,7 +19217,7 @@
         <v>14</v>
       </c>
       <c r="H626" t="n">
-        <v>0.4803215677540625</v>
+        <v>0.4208876822611241</v>
       </c>
     </row>
     <row r="627">
@@ -19247,7 +19247,7 @@
         <v>14</v>
       </c>
       <c r="H627" t="n">
-        <v>0.4431082576334383</v>
+        <v>0.5057590474361977</v>
       </c>
     </row>
     <row r="628">
@@ -19277,7 +19277,7 @@
         <v>8</v>
       </c>
       <c r="H628" t="n">
-        <v>0.3163667578219646</v>
+        <v>0.3257698340107862</v>
       </c>
     </row>
     <row r="629">
@@ -19307,7 +19307,7 @@
         <v>5</v>
       </c>
       <c r="H629" t="n">
-        <v>0.1552461368628965</v>
+        <v>0.09591772803864343</v>
       </c>
     </row>
   </sheetData>
